--- a/listas/output/Lista Papu.xlsx
+++ b/listas/output/Lista Papu.xlsx
@@ -43,7 +43,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Puertas Livianas'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'Puertas Placa'!$A1:$F32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'Puertas Placa'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'Recargos'!$A1:$C68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'Recargos'!$A1:$C69</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Recargos'!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="316">
   <si>
     <t>VENTANAS HERRERO</t>
   </si>
@@ -810,6 +810,12 @@
   </si>
   <si>
     <t>20%</t>
+  </si>
+  <si>
+    <t>RECARGO Tres Guias</t>
+  </si>
+  <si>
+    <t>25%</t>
   </si>
   <si>
     <t>RECARGO Natural</t>
@@ -2056,16 +2062,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="4">
-        <v>25209</v>
+        <v>26344</v>
       </c>
       <c r="C6" s="4">
-        <v>32388</v>
+        <v>33523</v>
       </c>
       <c r="D6" s="4">
         <v>9659</v>
       </c>
       <c r="E6" s="4">
-        <v>32772</v>
+        <v>34247</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2073,16 +2079,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="4">
-        <v>35935</v>
+        <v>36123</v>
       </c>
       <c r="C7" s="4">
-        <v>43114</v>
+        <v>43302</v>
       </c>
       <c r="D7" s="4">
         <v>10839</v>
       </c>
       <c r="E7" s="4">
-        <v>46716</v>
+        <v>46960</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2090,16 +2096,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="4">
-        <v>39483</v>
+        <v>39724</v>
       </c>
       <c r="C8" s="4">
-        <v>46662</v>
+        <v>46903</v>
       </c>
       <c r="D8" s="4">
         <v>12428</v>
       </c>
       <c r="E8" s="4">
-        <v>51328</v>
+        <v>51641</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2107,16 +2113,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="4">
-        <v>44208</v>
+        <v>44503</v>
       </c>
       <c r="C9" s="4">
-        <v>51387</v>
+        <v>51682</v>
       </c>
       <c r="D9" s="4">
         <v>14016</v>
       </c>
       <c r="E9" s="4">
-        <v>57470</v>
+        <v>57854</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2124,16 +2130,16 @@
         <v>10</v>
       </c>
       <c r="B10" s="4">
-        <v>51844</v>
+        <v>52219</v>
       </c>
       <c r="C10" s="4">
-        <v>59023</v>
+        <v>59398</v>
       </c>
       <c r="D10" s="4">
         <v>16399</v>
       </c>
       <c r="E10" s="4">
-        <v>67397</v>
+        <v>67885</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2141,16 +2147,16 @@
         <v>11</v>
       </c>
       <c r="B11" s="4">
-        <v>58338</v>
+        <v>58793</v>
       </c>
       <c r="C11" s="4">
-        <v>65517</v>
+        <v>65972</v>
       </c>
       <c r="D11" s="4">
         <v>18781</v>
       </c>
       <c r="E11" s="4">
-        <v>75839</v>
+        <v>76431</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2158,16 +2164,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="4">
-        <v>64791</v>
+        <v>65300</v>
       </c>
       <c r="C12" s="4">
-        <v>71970</v>
+        <v>72479</v>
       </c>
       <c r="D12" s="4">
         <v>20370</v>
       </c>
       <c r="E12" s="4">
-        <v>84228</v>
+        <v>84890</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2175,16 +2181,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="4">
-        <v>35734</v>
+        <v>35958</v>
       </c>
       <c r="C13" s="4">
-        <v>46502</v>
+        <v>46726</v>
       </c>
       <c r="D13" s="4">
         <v>12194</v>
       </c>
       <c r="E13" s="4">
-        <v>46454</v>
+        <v>46745</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2192,16 +2198,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="4">
-        <v>44070</v>
+        <v>44383</v>
       </c>
       <c r="C14" s="4">
-        <v>54838</v>
+        <v>55151</v>
       </c>
       <c r="D14" s="4">
         <v>14016</v>
       </c>
       <c r="E14" s="4">
-        <v>57291</v>
+        <v>57698</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2209,16 +2215,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="4">
-        <v>49068</v>
+        <v>49470</v>
       </c>
       <c r="C15" s="4">
-        <v>59836</v>
+        <v>60238</v>
       </c>
       <c r="D15" s="4">
         <v>15838</v>
       </c>
       <c r="E15" s="4">
-        <v>63788</v>
+        <v>64311</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2226,16 +2232,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="4">
-        <v>54357</v>
+        <v>54848</v>
       </c>
       <c r="C16" s="4">
-        <v>65125</v>
+        <v>65616</v>
       </c>
       <c r="D16" s="4">
         <v>17660</v>
       </c>
       <c r="E16" s="4">
-        <v>70664</v>
+        <v>71302</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2243,16 +2249,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>63094</v>
+        <v>63719</v>
       </c>
       <c r="C17" s="4">
-        <v>73862</v>
+        <v>74487</v>
       </c>
       <c r="D17" s="4">
         <v>20393</v>
       </c>
       <c r="E17" s="4">
-        <v>82022</v>
+        <v>82835</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2260,16 +2266,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>70662</v>
+        <v>71421</v>
       </c>
       <c r="C18" s="4">
-        <v>81430</v>
+        <v>82189</v>
       </c>
       <c r="D18" s="4">
         <v>23126</v>
       </c>
       <c r="E18" s="4">
-        <v>91861</v>
+        <v>92847</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2277,16 +2283,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>80418</v>
+        <v>81267</v>
       </c>
       <c r="C19" s="4">
-        <v>91186</v>
+        <v>92035</v>
       </c>
       <c r="D19" s="4">
         <v>24948</v>
       </c>
       <c r="E19" s="4">
-        <v>104543</v>
+        <v>105647</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2294,16 +2300,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="4">
-        <v>60689</v>
+        <v>61252</v>
       </c>
       <c r="C20" s="4">
-        <v>75047</v>
+        <v>75610</v>
       </c>
       <c r="D20" s="4">
         <v>19249</v>
       </c>
       <c r="E20" s="4">
-        <v>78896</v>
+        <v>79628</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2311,16 +2317,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="4">
-        <v>66267</v>
+        <v>66955</v>
       </c>
       <c r="C21" s="4">
-        <v>80625</v>
+        <v>81313</v>
       </c>
       <c r="D21" s="4">
         <v>21304</v>
       </c>
       <c r="E21" s="4">
-        <v>86147</v>
+        <v>87042</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2328,16 +2334,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="4">
-        <v>76078</v>
+        <v>76953</v>
       </c>
       <c r="C22" s="4">
-        <v>90436</v>
+        <v>91311</v>
       </c>
       <c r="D22" s="4">
         <v>24388</v>
       </c>
       <c r="E22" s="4">
-        <v>98901</v>
+        <v>100039</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2345,16 +2351,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="4">
-        <v>84153</v>
+        <v>85215</v>
       </c>
       <c r="C23" s="4">
-        <v>98511</v>
+        <v>99573</v>
       </c>
       <c r="D23" s="4">
         <v>27471</v>
       </c>
       <c r="E23" s="4">
-        <v>109399</v>
+        <v>110780</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2362,16 +2368,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="4">
-        <v>94953</v>
+        <v>96141</v>
       </c>
       <c r="C24" s="4">
-        <v>109311</v>
+        <v>110499</v>
       </c>
       <c r="D24" s="4">
         <v>29527</v>
       </c>
       <c r="E24" s="4">
-        <v>123439</v>
+        <v>124983</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2379,16 +2385,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="4">
-        <v>70118</v>
+        <v>70841</v>
       </c>
       <c r="C25" s="4">
-        <v>88064</v>
+        <v>88787</v>
       </c>
       <c r="D25" s="4">
         <v>22659</v>
       </c>
       <c r="E25" s="4">
-        <v>91153</v>
+        <v>92093</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2396,16 +2402,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="4">
-        <v>76184</v>
+        <v>77068</v>
       </c>
       <c r="C26" s="4">
-        <v>94130</v>
+        <v>95014</v>
       </c>
       <c r="D26" s="4">
         <v>24948</v>
       </c>
       <c r="E26" s="4">
-        <v>99039</v>
+        <v>100188</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2413,16 +2419,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="4">
-        <v>87310</v>
+        <v>88435</v>
       </c>
       <c r="C27" s="4">
-        <v>105256</v>
+        <v>106381</v>
       </c>
       <c r="D27" s="4">
         <v>28382</v>
       </c>
       <c r="E27" s="4">
-        <v>113503</v>
+        <v>114966</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2430,16 +2436,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="4">
-        <v>96457</v>
+        <v>97823</v>
       </c>
       <c r="C28" s="4">
-        <v>114403</v>
+        <v>115769</v>
       </c>
       <c r="D28" s="4">
         <v>31816</v>
       </c>
       <c r="E28" s="4">
-        <v>125394</v>
+        <v>127170</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2447,16 +2453,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="4">
-        <v>107990</v>
+        <v>109517</v>
       </c>
       <c r="C29" s="4">
-        <v>125936</v>
+        <v>127463</v>
       </c>
       <c r="D29" s="4">
         <v>34106</v>
       </c>
       <c r="E29" s="4">
-        <v>140387</v>
+        <v>142372</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2464,16 +2470,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="4">
-        <v>113702</v>
+        <v>115390</v>
       </c>
       <c r="C30" s="4">
-        <v>131648</v>
+        <v>133336</v>
       </c>
       <c r="D30" s="4">
         <v>36395</v>
       </c>
       <c r="E30" s="4">
-        <v>147813</v>
+        <v>150007</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2481,16 +2487,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="4">
-        <v>120575</v>
+        <v>122424</v>
       </c>
       <c r="C31" s="4">
-        <v>138521</v>
+        <v>140370</v>
       </c>
       <c r="D31" s="4">
         <v>38684</v>
       </c>
       <c r="E31" s="4">
-        <v>156748</v>
+        <v>159151</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2498,16 +2504,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="4">
-        <v>75433</v>
+        <v>76237</v>
       </c>
       <c r="C32" s="4">
-        <v>95174</v>
+        <v>95978</v>
       </c>
       <c r="D32" s="4">
         <v>24364</v>
       </c>
       <c r="E32" s="4">
-        <v>98063</v>
+        <v>99108</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2515,16 +2521,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="4">
-        <v>82661</v>
+        <v>83644</v>
       </c>
       <c r="C33" s="4">
-        <v>102402</v>
+        <v>103385</v>
       </c>
       <c r="D33" s="4">
         <v>26771</v>
       </c>
       <c r="E33" s="4">
-        <v>107459</v>
+        <v>108737</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2532,16 +2538,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="4">
-        <v>94156</v>
+        <v>95406</v>
       </c>
       <c r="C34" s="4">
-        <v>113897</v>
+        <v>115147</v>
       </c>
       <c r="D34" s="4">
         <v>30380</v>
       </c>
       <c r="E34" s="4">
-        <v>122403</v>
+        <v>124028</v>
       </c>
     </row>
     <row r="35" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2549,16 +2555,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="4">
-        <v>104433</v>
+        <v>105952</v>
       </c>
       <c r="C35" s="4">
-        <v>124174</v>
+        <v>125693</v>
       </c>
       <c r="D35" s="4">
         <v>33989</v>
       </c>
       <c r="E35" s="4">
-        <v>135763</v>
+        <v>137738</v>
       </c>
     </row>
     <row r="36" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2566,16 +2572,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="4">
-        <v>122541</v>
+        <v>124416</v>
       </c>
       <c r="C36" s="4">
-        <v>142282</v>
+        <v>144157</v>
       </c>
       <c r="D36" s="4">
         <v>41207</v>
       </c>
       <c r="E36" s="4">
-        <v>159303</v>
+        <v>161741</v>
       </c>
     </row>
     <row r="37" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2583,16 +2589,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="4">
-        <v>126147</v>
+        <v>128201</v>
       </c>
       <c r="C37" s="4">
-        <v>145888</v>
+        <v>147942</v>
       </c>
       <c r="D37" s="4">
         <v>41207</v>
       </c>
       <c r="E37" s="4">
-        <v>163991</v>
+        <v>166661</v>
       </c>
     </row>
     <row r="38" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2600,16 +2606,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="4">
-        <v>79624</v>
+        <v>80508</v>
       </c>
       <c r="C38" s="4">
-        <v>101159</v>
+        <v>102043</v>
       </c>
       <c r="D38" s="4">
         <v>26070</v>
       </c>
       <c r="E38" s="4">
-        <v>103511</v>
+        <v>104660</v>
       </c>
     </row>
     <row r="39" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2617,16 +2623,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="4">
-        <v>87217</v>
+        <v>88297</v>
       </c>
       <c r="C39" s="4">
-        <v>108752</v>
+        <v>109832</v>
       </c>
       <c r="D39" s="4">
         <v>28593</v>
       </c>
       <c r="E39" s="4">
-        <v>113382</v>
+        <v>114786</v>
       </c>
     </row>
     <row r="40" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2634,16 +2640,16 @@
         <v>40</v>
       </c>
       <c r="B40" s="4">
-        <v>99197</v>
+        <v>100572</v>
       </c>
       <c r="C40" s="4">
-        <v>120732</v>
+        <v>122107</v>
       </c>
       <c r="D40" s="4">
         <v>32377</v>
       </c>
       <c r="E40" s="4">
-        <v>128956</v>
+        <v>130744</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2651,16 +2657,16 @@
         <v>41</v>
       </c>
       <c r="B41" s="4">
-        <v>110008</v>
+        <v>111678</v>
       </c>
       <c r="C41" s="4">
-        <v>131543</v>
+        <v>133213</v>
       </c>
       <c r="D41" s="4">
         <v>36161</v>
       </c>
       <c r="E41" s="4">
-        <v>143010</v>
+        <v>145181</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2668,16 +2674,16 @@
         <v>42</v>
       </c>
       <c r="B42" s="4">
-        <v>121046</v>
+        <v>122912</v>
       </c>
       <c r="C42" s="4">
-        <v>142581</v>
+        <v>144447</v>
       </c>
       <c r="D42" s="4">
         <v>38684</v>
       </c>
       <c r="E42" s="4">
-        <v>157360</v>
+        <v>159786</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2685,16 +2691,16 @@
         <v>43</v>
       </c>
       <c r="B43" s="4">
-        <v>128696</v>
+        <v>130759</v>
       </c>
       <c r="C43" s="4">
-        <v>150231</v>
+        <v>152294</v>
       </c>
       <c r="D43" s="4">
         <v>41207</v>
       </c>
       <c r="E43" s="4">
-        <v>167305</v>
+        <v>169987</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2702,16 +2708,16 @@
         <v>44</v>
       </c>
       <c r="B44" s="4">
-        <v>134833</v>
+        <v>137093</v>
       </c>
       <c r="C44" s="4">
-        <v>156368</v>
+        <v>158628</v>
       </c>
       <c r="D44" s="4">
         <v>43730</v>
       </c>
       <c r="E44" s="4">
-        <v>175283</v>
+        <v>178221</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2719,16 +2725,16 @@
         <v>45</v>
       </c>
       <c r="B45" s="4">
-        <v>93141</v>
+        <v>94266</v>
       </c>
       <c r="C45" s="4">
-        <v>120060</v>
+        <v>121185</v>
       </c>
       <c r="D45" s="4">
         <v>31186</v>
       </c>
       <c r="E45" s="4">
-        <v>121083</v>
+        <v>122546</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2736,16 +2742,16 @@
         <v>46</v>
       </c>
       <c r="B46" s="4">
-        <v>101822</v>
+        <v>103197</v>
       </c>
       <c r="C46" s="4">
-        <v>128741</v>
+        <v>130116</v>
       </c>
       <c r="D46" s="4">
         <v>34059</v>
       </c>
       <c r="E46" s="4">
-        <v>132369</v>
+        <v>134156</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2753,16 +2759,16 @@
         <v>47</v>
       </c>
       <c r="B47" s="4">
-        <v>115417</v>
+        <v>117167</v>
       </c>
       <c r="C47" s="4">
-        <v>142336</v>
+        <v>144086</v>
       </c>
       <c r="D47" s="4">
         <v>38369</v>
       </c>
       <c r="E47" s="4">
-        <v>150042</v>
+        <v>152317</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2770,16 +2776,16 @@
         <v>48</v>
       </c>
       <c r="B48" s="4">
-        <v>126695</v>
+        <v>128820</v>
       </c>
       <c r="C48" s="4">
-        <v>153614</v>
+        <v>155739</v>
       </c>
       <c r="D48" s="4">
         <v>42679</v>
       </c>
       <c r="E48" s="4">
-        <v>164704</v>
+        <v>167466</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2787,16 +2793,16 @@
         <v>49</v>
       </c>
       <c r="B49" s="4">
-        <v>139672</v>
+        <v>142047</v>
       </c>
       <c r="C49" s="4">
-        <v>166591</v>
+        <v>168966</v>
       </c>
       <c r="D49" s="4">
         <v>45552</v>
       </c>
       <c r="E49" s="4">
-        <v>181574</v>
+        <v>184661</v>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2804,16 +2810,16 @@
         <v>50</v>
       </c>
       <c r="B50" s="4">
-        <v>147538</v>
+        <v>150163</v>
       </c>
       <c r="C50" s="4">
-        <v>174457</v>
+        <v>177082</v>
       </c>
       <c r="D50" s="4">
         <v>48425</v>
       </c>
       <c r="E50" s="4">
-        <v>191799</v>
+        <v>195212</v>
       </c>
     </row>
     <row r="51" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2821,16 +2827,16 @@
         <v>51</v>
       </c>
       <c r="B51" s="4">
-        <v>156223</v>
+        <v>159099</v>
       </c>
       <c r="C51" s="4">
-        <v>183142</v>
+        <v>186018</v>
       </c>
       <c r="D51" s="4">
         <v>51299</v>
       </c>
       <c r="E51" s="4">
-        <v>203090</v>
+        <v>206829</v>
       </c>
     </row>
     <row r="52" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2838,16 +2844,16 @@
         <v>52</v>
       </c>
       <c r="B52" s="4">
-        <v>121816</v>
+        <v>123343</v>
       </c>
       <c r="C52" s="4">
-        <v>157709</v>
+        <v>159236</v>
       </c>
       <c r="D52" s="4">
         <v>39712</v>
       </c>
       <c r="E52" s="4">
-        <v>158361</v>
+        <v>160346</v>
       </c>
     </row>
     <row r="53" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2855,16 +2861,16 @@
         <v>53</v>
       </c>
       <c r="B53" s="4">
-        <v>135105</v>
+        <v>136971</v>
       </c>
       <c r="C53" s="4">
-        <v>170998</v>
+        <v>172864</v>
       </c>
       <c r="D53" s="4">
         <v>43169</v>
       </c>
       <c r="E53" s="4">
-        <v>175637</v>
+        <v>178062</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2872,16 +2878,16 @@
         <v>54</v>
       </c>
       <c r="B54" s="4">
-        <v>157229</v>
+        <v>159729</v>
       </c>
       <c r="C54" s="4">
-        <v>193122</v>
+        <v>195622</v>
       </c>
       <c r="D54" s="4">
         <v>48355</v>
       </c>
       <c r="E54" s="4">
-        <v>204398</v>
+        <v>207648</v>
       </c>
     </row>
     <row r="55" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2889,16 +2895,16 @@
         <v>55</v>
       </c>
       <c r="B55" s="4">
-        <v>175793</v>
+        <v>178829</v>
       </c>
       <c r="C55" s="4">
-        <v>211686</v>
+        <v>214722</v>
       </c>
       <c r="D55" s="4">
         <v>53541</v>
       </c>
       <c r="E55" s="4">
-        <v>228531</v>
+        <v>232478</v>
       </c>
     </row>
     <row r="56" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2906,16 +2912,16 @@
         <v>56</v>
       </c>
       <c r="B56" s="4">
-        <v>190401</v>
+        <v>193795</v>
       </c>
       <c r="C56" s="4">
-        <v>226294</v>
+        <v>229688</v>
       </c>
       <c r="D56" s="4">
         <v>56998</v>
       </c>
       <c r="E56" s="4">
-        <v>247521</v>
+        <v>251934</v>
       </c>
     </row>
     <row r="57" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2923,16 +2929,16 @@
         <v>57</v>
       </c>
       <c r="B57" s="4">
-        <v>204937</v>
+        <v>208687</v>
       </c>
       <c r="C57" s="4">
-        <v>240830</v>
+        <v>244580</v>
       </c>
       <c r="D57" s="4">
         <v>60456</v>
       </c>
       <c r="E57" s="4">
-        <v>266418</v>
+        <v>271293</v>
       </c>
     </row>
     <row r="58" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2940,16 +2946,16 @@
         <v>58</v>
       </c>
       <c r="B58" s="4">
-        <v>217179</v>
+        <v>221287</v>
       </c>
       <c r="C58" s="4">
-        <v>253072</v>
+        <v>257180</v>
       </c>
       <c r="D58" s="4">
         <v>63913</v>
       </c>
       <c r="E58" s="4">
-        <v>282333</v>
+        <v>287673</v>
       </c>
     </row>
     <row r="59" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2957,16 +2963,16 @@
         <v>59</v>
       </c>
       <c r="B59" s="4">
-        <v>228038</v>
+        <v>232351</v>
       </c>
       <c r="C59" s="4">
-        <v>265726</v>
+        <v>270039</v>
       </c>
       <c r="D59" s="4">
         <v>67109</v>
       </c>
       <c r="E59" s="4">
-        <v>296449</v>
+        <v>302056</v>
       </c>
     </row>
   </sheetData>
@@ -3733,10 +3739,10 @@
         <v>169</v>
       </c>
       <c r="C6" s="4">
-        <v>143354</v>
+        <v>144764</v>
       </c>
       <c r="D6" s="4">
-        <v>146069</v>
+        <v>147620</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3747,10 +3753,10 @@
         <v>169</v>
       </c>
       <c r="C7" s="4">
-        <v>132263</v>
+        <v>132187</v>
       </c>
       <c r="D7" s="4">
-        <v>134978</v>
+        <v>134884</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3758,13 +3764,13 @@
         <v>172</v>
       </c>
       <c r="B8" s="4">
-        <v>151017</v>
+        <v>151568</v>
       </c>
       <c r="C8" s="4">
-        <v>153256</v>
+        <v>153924</v>
       </c>
       <c r="D8" s="4">
-        <v>154537</v>
+        <v>155272</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3772,13 +3778,13 @@
         <v>226</v>
       </c>
       <c r="B9" s="4">
-        <v>178582</v>
+        <v>179133</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>169</v>
       </c>
       <c r="D9" s="4">
-        <v>182102</v>
+        <v>182837</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3786,13 +3792,13 @@
         <v>174</v>
       </c>
       <c r="B10" s="4">
-        <v>163778</v>
+        <v>164086</v>
       </c>
       <c r="C10" s="4">
-        <v>164984</v>
+        <v>165355</v>
       </c>
       <c r="D10" s="4">
-        <v>165700</v>
+        <v>166109</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3800,13 +3806,13 @@
         <v>175</v>
       </c>
       <c r="B11" s="4">
-        <v>177752</v>
+        <v>178060</v>
       </c>
       <c r="C11" s="4">
-        <v>178958</v>
+        <v>179329</v>
       </c>
       <c r="D11" s="4">
-        <v>179674</v>
+        <v>180083</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3893,10 +3899,10 @@
         <v>235</v>
       </c>
       <c r="D6" s="4">
-        <v>76300</v>
+        <v>80200</v>
       </c>
       <c r="E6" s="4">
-        <v>81100</v>
+        <v>85200</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>169</v>
@@ -3913,10 +3919,10 @@
         <v>236</v>
       </c>
       <c r="D7" s="4">
-        <v>76300</v>
+        <v>80200</v>
       </c>
       <c r="E7" s="4">
-        <v>81100</v>
+        <v>85200</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>169</v>
@@ -3933,10 +3939,10 @@
         <v>237</v>
       </c>
       <c r="D8" s="4">
-        <v>81100</v>
+        <v>85200</v>
       </c>
       <c r="E8" s="4">
-        <v>86112</v>
+        <v>90420</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>169</v>
@@ -4079,7 +4085,7 @@
         <v>169</v>
       </c>
       <c r="F15" s="4">
-        <v>79500</v>
+        <v>83500</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4099,7 +4105,7 @@
         <v>169</v>
       </c>
       <c r="F16" s="4">
-        <v>79500</v>
+        <v>83500</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4119,7 +4125,7 @@
         <v>169</v>
       </c>
       <c r="F17" s="4">
-        <v>82600</v>
+        <v>86730</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4193,10 +4199,10 @@
         <v>235</v>
       </c>
       <c r="D21" s="4">
-        <v>228900</v>
+        <v>240345</v>
       </c>
       <c r="E21" s="4">
-        <v>228900</v>
+        <v>240345</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>169</v>
@@ -4213,10 +4219,10 @@
         <v>236</v>
       </c>
       <c r="D22" s="4">
-        <v>228900</v>
+        <v>240345</v>
       </c>
       <c r="E22" s="4">
-        <v>228900</v>
+        <v>240345</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>169</v>
@@ -4233,10 +4239,10 @@
         <v>237</v>
       </c>
       <c r="D23" s="4">
-        <v>244500</v>
+        <v>256725</v>
       </c>
       <c r="E23" s="4">
-        <v>244500</v>
+        <v>256725</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>169</v>
@@ -4378,7 +4384,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="13" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -4459,18 +4465,18 @@
         <v>249</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>249</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4478,334 +4484,334 @@
         <v>260</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C12" s="4">
-        <v>10685</v>
+        <v>249</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C13" s="4">
-        <v>18080</v>
+        <v>10685</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C14" s="4">
-        <v>7400</v>
+        <v>18622</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C15" s="4">
-        <v>4200</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C16" s="4">
-        <v>13517</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C17" s="4">
-        <v>20505</v>
+        <v>13517</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C18" s="4">
-        <v>5905</v>
+        <v>21120</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C19" s="4">
-        <v>18500</v>
+        <v>5905</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C20" s="4">
-        <v>48364</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C21" s="4">
-        <v>346865</v>
+        <v>48364</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C22" s="4">
-        <v>280585</v>
+        <v>346865</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C23" s="4">
-        <v>346865</v>
+        <v>280585</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C24" s="4">
-        <v>30208</v>
+        <v>346865</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C25" s="4">
-        <v>23180</v>
+        <v>30208</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C26" s="4">
-        <v>37410</v>
+        <v>23180</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C27" s="4">
-        <v>28263</v>
+        <v>37410</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C28" s="4">
-        <v>52671</v>
+        <v>28263</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C29" s="4">
-        <v>39099</v>
+        <v>52671</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C30" s="4">
-        <v>188750</v>
+        <v>39099</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C31" s="4">
-        <v>139851</v>
+        <v>188750</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C32" s="4">
-        <v>204007</v>
+        <v>139851</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C33" s="4">
-        <v>155108</v>
+        <v>204007</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C34" s="4">
-        <v>25000</v>
+        <v>155108</v>
       </c>
     </row>
     <row r="35" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C35" s="4">
-        <v>45000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="36" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C36" s="4">
-        <v>100000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="37" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C37" s="4">
-        <v>4000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="38" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C38" s="4">
-        <v>4000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="39" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C39" s="4">
-        <v>4000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="40" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C40" s="4">
-        <v>5000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C41" s="4">
-        <v>18000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>247</v>
@@ -4816,117 +4822,117 @@
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C43" s="4">
-        <v>550000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C44" s="4">
-        <v>400000</v>
+        <v>550000</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C45" s="4">
-        <v>850000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C46" s="4">
-        <v>600000</v>
+        <v>850000</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C47" s="4">
-        <v>4500</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C48" s="4">
-        <v>250000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C49" s="4">
-        <v>5000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C50" s="4">
-        <v>13000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="51" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C51" s="4">
-        <v>11500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="52" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C52" s="4">
-        <v>0</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="53" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>247</v>
@@ -4937,133 +4943,144 @@
     </row>
     <row r="54" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C54" s="4">
-        <v>101970</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C55" s="4">
-        <v>112167</v>
+        <v>101970</v>
       </c>
     </row>
     <row r="56" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C56" s="4">
-        <v>17447</v>
+        <v>112167</v>
       </c>
     </row>
     <row r="57" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C57" s="4">
-        <v>22525</v>
+        <v>18319</v>
       </c>
     </row>
     <row r="58" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C58" s="4">
-        <v>28799</v>
+        <v>23651</v>
       </c>
     </row>
     <row r="59" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C59" s="4">
-        <v>35415</v>
+        <v>30239</v>
       </c>
     </row>
     <row r="60" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C60" s="4">
-        <v>28633</v>
+        <v>37186</v>
       </c>
     </row>
     <row r="61" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C61" s="4">
-        <v>64445</v>
+        <v>30065</v>
       </c>
     </row>
     <row r="62" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C62" s="4">
-        <v>69479</v>
+        <v>67667</v>
       </c>
     </row>
     <row r="63" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C63" s="4">
-        <v>77614</v>
+        <v>72258</v>
       </c>
     </row>
     <row r="64" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C64" s="4">
-        <v>93890</v>
+        <v>80719</v>
       </c>
     </row>
     <row r="65" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C65" s="4">
+        <v>97646</v>
+      </c>
+    </row>
+    <row r="66" ht="13" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C66" s="4">
         <v>12600</v>
       </c>
     </row>
@@ -5608,22 +5625,22 @@
         <v>99</v>
       </c>
       <c r="B6" s="4">
-        <v>34745</v>
+        <v>34878</v>
       </c>
       <c r="C6" s="4">
-        <v>35295</v>
+        <v>35455</v>
       </c>
       <c r="D6" s="4">
-        <v>36292</v>
+        <v>36504</v>
       </c>
       <c r="E6" s="4">
-        <v>41118</v>
+        <v>41576</v>
       </c>
       <c r="F6" s="4">
-        <v>35610</v>
+        <v>35787</v>
       </c>
       <c r="G6" s="4">
-        <v>45562</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5631,22 +5648,22 @@
         <v>100</v>
       </c>
       <c r="B7" s="4">
-        <v>37824</v>
+        <v>38001</v>
       </c>
       <c r="C7" s="4">
-        <v>38557</v>
+        <v>38771</v>
       </c>
       <c r="D7" s="4">
-        <v>39891</v>
+        <v>40173</v>
       </c>
       <c r="E7" s="4">
-        <v>46325</v>
+        <v>46936</v>
       </c>
       <c r="F7" s="4">
-        <v>38985</v>
+        <v>39221</v>
       </c>
       <c r="G7" s="4">
-        <v>52259</v>
+        <v>53174</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5654,22 +5671,22 @@
         <v>101</v>
       </c>
       <c r="B8" s="4">
-        <v>40910</v>
+        <v>41131</v>
       </c>
       <c r="C8" s="4">
-        <v>41826</v>
+        <v>42094</v>
       </c>
       <c r="D8" s="4">
-        <v>43495</v>
+        <v>43848</v>
       </c>
       <c r="E8" s="4">
-        <v>51537</v>
+        <v>52301</v>
       </c>
       <c r="F8" s="4">
-        <v>42365</v>
+        <v>42661</v>
       </c>
       <c r="G8" s="4">
-        <v>58963</v>
+        <v>60106</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5677,22 +5694,22 @@
         <v>102</v>
       </c>
       <c r="B9" s="4">
-        <v>43989</v>
+        <v>44254</v>
       </c>
       <c r="C9" s="4">
-        <v>45088</v>
+        <v>45410</v>
       </c>
       <c r="D9" s="4">
-        <v>47094</v>
+        <v>47518</v>
       </c>
       <c r="E9" s="4">
-        <v>56744</v>
+        <v>57661</v>
       </c>
       <c r="F9" s="4">
-        <v>45740</v>
+        <v>46094</v>
       </c>
       <c r="G9" s="4">
-        <v>65660</v>
+        <v>67032</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5700,22 +5717,22 @@
         <v>103</v>
       </c>
       <c r="B10" s="4">
-        <v>47068</v>
+        <v>47378</v>
       </c>
       <c r="C10" s="4">
-        <v>48351</v>
+        <v>48726</v>
       </c>
       <c r="D10" s="4">
-        <v>50692</v>
+        <v>51187</v>
       </c>
       <c r="E10" s="4">
-        <v>61951</v>
+        <v>63021</v>
       </c>
       <c r="F10" s="4">
-        <v>49114</v>
+        <v>49528</v>
       </c>
       <c r="G10" s="4">
-        <v>72357</v>
+        <v>73958</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5723,22 +5740,22 @@
         <v>104</v>
       </c>
       <c r="B11" s="4">
-        <v>50147</v>
+        <v>50501</v>
       </c>
       <c r="C11" s="4">
-        <v>51613</v>
+        <v>52042</v>
       </c>
       <c r="D11" s="4">
-        <v>54291</v>
+        <v>54856</v>
       </c>
       <c r="E11" s="4">
-        <v>67158</v>
+        <v>68381</v>
       </c>
       <c r="F11" s="4">
-        <v>52489</v>
+        <v>52962</v>
       </c>
       <c r="G11" s="4">
-        <v>79055</v>
+        <v>80885</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5746,22 +5763,22 @@
         <v>105</v>
       </c>
       <c r="B12" s="4">
-        <v>53227</v>
+        <v>53625</v>
       </c>
       <c r="C12" s="4">
-        <v>54876</v>
+        <v>55358</v>
       </c>
       <c r="D12" s="4">
-        <v>57889</v>
+        <v>58525</v>
       </c>
       <c r="E12" s="4">
-        <v>72365</v>
+        <v>73741</v>
       </c>
       <c r="F12" s="4">
-        <v>55863</v>
+        <v>56396</v>
       </c>
       <c r="G12" s="4">
-        <v>85752</v>
+        <v>87811</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5769,22 +5786,22 @@
         <v>106</v>
       </c>
       <c r="B13" s="4">
-        <v>37824</v>
+        <v>38001</v>
       </c>
       <c r="C13" s="4">
-        <v>38557</v>
+        <v>38771</v>
       </c>
       <c r="D13" s="4">
-        <v>39891</v>
+        <v>40173</v>
       </c>
       <c r="E13" s="4">
-        <v>46325</v>
+        <v>46936</v>
       </c>
       <c r="F13" s="4">
-        <v>38985</v>
+        <v>39221</v>
       </c>
       <c r="G13" s="4">
-        <v>52259</v>
+        <v>53174</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5792,22 +5809,22 @@
         <v>107</v>
       </c>
       <c r="B14" s="4">
-        <v>41205</v>
+        <v>41441</v>
       </c>
       <c r="C14" s="4">
-        <v>42172</v>
+        <v>42457</v>
       </c>
       <c r="D14" s="4">
-        <v>43964</v>
+        <v>44341</v>
       </c>
       <c r="E14" s="4">
-        <v>52525</v>
+        <v>53339</v>
       </c>
       <c r="F14" s="4">
-        <v>42742</v>
+        <v>43057</v>
       </c>
       <c r="G14" s="4">
-        <v>60441</v>
+        <v>61660</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5815,22 +5832,22 @@
         <v>108</v>
       </c>
       <c r="B15" s="4">
-        <v>44569</v>
+        <v>44864</v>
       </c>
       <c r="C15" s="4">
-        <v>45780</v>
+        <v>46137</v>
       </c>
       <c r="D15" s="4">
-        <v>48030</v>
+        <v>48502</v>
       </c>
       <c r="E15" s="4">
-        <v>58719</v>
+        <v>59737</v>
       </c>
       <c r="F15" s="4">
-        <v>46493</v>
+        <v>46886</v>
       </c>
       <c r="G15" s="4">
-        <v>68616</v>
+        <v>70139</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5838,22 +5855,22 @@
         <v>109</v>
       </c>
       <c r="B16" s="4">
-        <v>47933</v>
+        <v>48287</v>
       </c>
       <c r="C16" s="4">
-        <v>49389</v>
+        <v>49817</v>
       </c>
       <c r="D16" s="4">
-        <v>52097</v>
+        <v>52663</v>
       </c>
       <c r="E16" s="4">
-        <v>64914</v>
+        <v>66135</v>
       </c>
       <c r="F16" s="4">
-        <v>50244</v>
+        <v>50716</v>
       </c>
       <c r="G16" s="4">
-        <v>76792</v>
+        <v>78619</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5861,22 +5878,22 @@
         <v>110</v>
       </c>
       <c r="B17" s="4">
-        <v>51308</v>
+        <v>51721</v>
       </c>
       <c r="C17" s="4">
-        <v>52998</v>
+        <v>53497</v>
       </c>
       <c r="D17" s="4">
-        <v>56164</v>
+        <v>56825</v>
       </c>
       <c r="E17" s="4">
-        <v>71108</v>
+        <v>72532</v>
       </c>
       <c r="F17" s="4">
-        <v>53995</v>
+        <v>54546</v>
       </c>
       <c r="G17" s="4">
-        <v>84967</v>
+        <v>87099</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5884,22 +5901,22 @@
         <v>111</v>
       </c>
       <c r="B18" s="4">
-        <v>54672</v>
+        <v>55144</v>
       </c>
       <c r="C18" s="4">
-        <v>56606</v>
+        <v>57177</v>
       </c>
       <c r="D18" s="4">
-        <v>60231</v>
+        <v>60986</v>
       </c>
       <c r="E18" s="4">
-        <v>77302</v>
+        <v>78930</v>
       </c>
       <c r="F18" s="4">
-        <v>57747</v>
+        <v>58375</v>
       </c>
       <c r="G18" s="4">
-        <v>93142</v>
+        <v>95579</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5907,22 +5924,22 @@
         <v>112</v>
       </c>
       <c r="B19" s="4">
-        <v>58037</v>
+        <v>58567</v>
       </c>
       <c r="C19" s="4">
-        <v>60215</v>
+        <v>60857</v>
       </c>
       <c r="D19" s="4">
-        <v>64297</v>
+        <v>65148</v>
       </c>
       <c r="E19" s="4">
-        <v>83497</v>
+        <v>85328</v>
       </c>
       <c r="F19" s="4">
-        <v>61498</v>
+        <v>62205</v>
       </c>
       <c r="G19" s="4">
-        <v>101318</v>
+        <v>104059</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5930,22 +5947,22 @@
         <v>113</v>
       </c>
       <c r="B20" s="4">
-        <v>40910</v>
+        <v>41131</v>
       </c>
       <c r="C20" s="4">
-        <v>41826</v>
+        <v>42094</v>
       </c>
       <c r="D20" s="4">
-        <v>43495</v>
+        <v>43848</v>
       </c>
       <c r="E20" s="4">
-        <v>51537</v>
+        <v>52301</v>
       </c>
       <c r="F20" s="4">
-        <v>42365</v>
+        <v>42661</v>
       </c>
       <c r="G20" s="4">
-        <v>58963</v>
+        <v>60106</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5953,22 +5970,22 @@
         <v>114</v>
       </c>
       <c r="B21" s="4">
-        <v>44569</v>
+        <v>44864</v>
       </c>
       <c r="C21" s="4">
-        <v>45780</v>
+        <v>46137</v>
       </c>
       <c r="D21" s="4">
-        <v>48030</v>
+        <v>48502</v>
       </c>
       <c r="E21" s="4">
-        <v>58719</v>
+        <v>59737</v>
       </c>
       <c r="F21" s="4">
-        <v>46493</v>
+        <v>46886</v>
       </c>
       <c r="G21" s="4">
-        <v>68616</v>
+        <v>70139</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5976,22 +5993,22 @@
         <v>115</v>
       </c>
       <c r="B22" s="4">
-        <v>48218</v>
+        <v>48587</v>
       </c>
       <c r="C22" s="4">
-        <v>49735</v>
+        <v>50181</v>
       </c>
       <c r="D22" s="4">
-        <v>52565</v>
+        <v>53156</v>
       </c>
       <c r="E22" s="4">
-        <v>65901</v>
+        <v>67173</v>
       </c>
       <c r="F22" s="4">
-        <v>50621</v>
+        <v>51112</v>
       </c>
       <c r="G22" s="4">
-        <v>78270</v>
+        <v>80173</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5999,22 +6016,22 @@
         <v>116</v>
       </c>
       <c r="B23" s="4">
-        <v>51878</v>
+        <v>52320</v>
       </c>
       <c r="C23" s="4">
-        <v>53690</v>
+        <v>54225</v>
       </c>
       <c r="D23" s="4">
-        <v>57100</v>
+        <v>57809</v>
       </c>
       <c r="E23" s="4">
-        <v>73185</v>
+        <v>74715</v>
       </c>
       <c r="F23" s="4">
-        <v>54749</v>
+        <v>55337</v>
       </c>
       <c r="G23" s="4">
-        <v>87923</v>
+        <v>90207</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6022,22 +6039,22 @@
         <v>117</v>
       </c>
       <c r="B24" s="4">
-        <v>55538</v>
+        <v>56053</v>
       </c>
       <c r="C24" s="4">
-        <v>57645</v>
+        <v>58268</v>
       </c>
       <c r="D24" s="4">
-        <v>61635</v>
+        <v>62463</v>
       </c>
       <c r="E24" s="4">
-        <v>80468</v>
+        <v>82258</v>
       </c>
       <c r="F24" s="4">
-        <v>58877</v>
+        <v>59563</v>
       </c>
       <c r="G24" s="4">
-        <v>97577</v>
+        <v>100240</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6045,22 +6062,22 @@
         <v>118</v>
       </c>
       <c r="B25" s="4">
-        <v>59197</v>
+        <v>59787</v>
       </c>
       <c r="C25" s="4">
-        <v>61600</v>
+        <v>62312</v>
       </c>
       <c r="D25" s="4">
-        <v>66170</v>
+        <v>67116</v>
       </c>
       <c r="E25" s="4">
-        <v>87752</v>
+        <v>89800</v>
       </c>
       <c r="F25" s="4">
-        <v>63004</v>
+        <v>63789</v>
       </c>
       <c r="G25" s="4">
-        <v>107230</v>
+        <v>110274</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6068,22 +6085,22 @@
         <v>119</v>
       </c>
       <c r="B26" s="4">
-        <v>62857</v>
+        <v>63520</v>
       </c>
       <c r="C26" s="4">
-        <v>65554</v>
+        <v>66356</v>
       </c>
       <c r="D26" s="4">
-        <v>70705</v>
+        <v>71770</v>
       </c>
       <c r="E26" s="4">
-        <v>95036</v>
+        <v>97343</v>
       </c>
       <c r="F26" s="4">
-        <v>67132</v>
+        <v>68014</v>
       </c>
       <c r="G26" s="4">
-        <v>116884</v>
+        <v>120307</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6091,22 +6108,22 @@
         <v>120</v>
       </c>
       <c r="B27" s="4">
-        <v>43989</v>
+        <v>44254</v>
       </c>
       <c r="C27" s="4">
-        <v>45088</v>
+        <v>45410</v>
       </c>
       <c r="D27" s="4">
-        <v>47094</v>
+        <v>47518</v>
       </c>
       <c r="E27" s="4">
-        <v>56744</v>
+        <v>57661</v>
       </c>
       <c r="F27" s="4">
-        <v>45740</v>
+        <v>46094</v>
       </c>
       <c r="G27" s="4">
-        <v>65660</v>
+        <v>67032</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6114,22 +6131,22 @@
         <v>121</v>
       </c>
       <c r="B28" s="4">
-        <v>47933</v>
+        <v>48287</v>
       </c>
       <c r="C28" s="4">
-        <v>49389</v>
+        <v>49817</v>
       </c>
       <c r="D28" s="4">
-        <v>52097</v>
+        <v>52663</v>
       </c>
       <c r="E28" s="4">
-        <v>64914</v>
+        <v>66135</v>
       </c>
       <c r="F28" s="4">
-        <v>50244</v>
+        <v>50716</v>
       </c>
       <c r="G28" s="4">
-        <v>76792</v>
+        <v>78619</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6137,22 +6154,22 @@
         <v>122</v>
       </c>
       <c r="B29" s="4">
-        <v>51878</v>
+        <v>52320</v>
       </c>
       <c r="C29" s="4">
-        <v>53690</v>
+        <v>54225</v>
       </c>
       <c r="D29" s="4">
-        <v>57100</v>
+        <v>57809</v>
       </c>
       <c r="E29" s="4">
-        <v>73185</v>
+        <v>74715</v>
       </c>
       <c r="F29" s="4">
-        <v>54749</v>
+        <v>55337</v>
       </c>
       <c r="G29" s="4">
-        <v>87923</v>
+        <v>90207</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6160,22 +6177,22 @@
         <v>123</v>
       </c>
       <c r="B30" s="4">
-        <v>55833</v>
+        <v>56364</v>
       </c>
       <c r="C30" s="4">
-        <v>57991</v>
+        <v>58632</v>
       </c>
       <c r="D30" s="4">
-        <v>62104</v>
+        <v>62955</v>
       </c>
       <c r="E30" s="4">
-        <v>81456</v>
+        <v>83296</v>
       </c>
       <c r="F30" s="4">
-        <v>59253</v>
+        <v>59959</v>
       </c>
       <c r="G30" s="4">
-        <v>99055</v>
+        <v>101794</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6183,22 +6200,22 @@
         <v>124</v>
       </c>
       <c r="B31" s="4">
-        <v>59777</v>
+        <v>60397</v>
       </c>
       <c r="C31" s="4">
-        <v>62292</v>
+        <v>63040</v>
       </c>
       <c r="D31" s="4">
-        <v>67107</v>
+        <v>68101</v>
       </c>
       <c r="E31" s="4">
-        <v>89727</v>
+        <v>91876</v>
       </c>
       <c r="F31" s="4">
-        <v>63758</v>
+        <v>64580</v>
       </c>
       <c r="G31" s="4">
-        <v>110187</v>
+        <v>113381</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6206,22 +6223,22 @@
         <v>125</v>
       </c>
       <c r="B32" s="4">
-        <v>63722</v>
+        <v>64430</v>
       </c>
       <c r="C32" s="4">
-        <v>66593</v>
+        <v>67447</v>
       </c>
       <c r="D32" s="4">
-        <v>72110</v>
+        <v>73247</v>
       </c>
       <c r="E32" s="4">
-        <v>97998</v>
+        <v>100457</v>
       </c>
       <c r="F32" s="4">
-        <v>68262</v>
+        <v>69202</v>
       </c>
       <c r="G32" s="4">
-        <v>121318</v>
+        <v>124968</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6229,22 +6246,22 @@
         <v>126</v>
       </c>
       <c r="B33" s="4">
-        <v>67667</v>
+        <v>68463</v>
       </c>
       <c r="C33" s="4">
-        <v>70894</v>
+        <v>71855</v>
       </c>
       <c r="D33" s="4">
-        <v>77114</v>
+        <v>78392</v>
       </c>
       <c r="E33" s="4">
-        <v>106269</v>
+        <v>109037</v>
       </c>
       <c r="F33" s="4">
-        <v>72767</v>
+        <v>73823</v>
       </c>
       <c r="G33" s="4">
-        <v>132450</v>
+        <v>136555</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6252,22 +6269,22 @@
         <v>127</v>
       </c>
       <c r="B34" s="4">
-        <v>47068</v>
+        <v>47378</v>
       </c>
       <c r="C34" s="4">
-        <v>48351</v>
+        <v>48726</v>
       </c>
       <c r="D34" s="4">
-        <v>50692</v>
+        <v>51187</v>
       </c>
       <c r="E34" s="4">
-        <v>61951</v>
+        <v>63021</v>
       </c>
       <c r="F34" s="4">
-        <v>49114</v>
+        <v>49528</v>
       </c>
       <c r="G34" s="4">
-        <v>72357</v>
+        <v>73958</v>
       </c>
     </row>
     <row r="35" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6275,22 +6292,22 @@
         <v>128</v>
       </c>
       <c r="B35" s="4">
-        <v>51308</v>
+        <v>51721</v>
       </c>
       <c r="C35" s="4">
-        <v>52998</v>
+        <v>53497</v>
       </c>
       <c r="D35" s="4">
-        <v>56164</v>
+        <v>56825</v>
       </c>
       <c r="E35" s="4">
-        <v>71108</v>
+        <v>72532</v>
       </c>
       <c r="F35" s="4">
-        <v>53995</v>
+        <v>54546</v>
       </c>
       <c r="G35" s="4">
-        <v>84967</v>
+        <v>87099</v>
       </c>
     </row>
     <row r="36" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6298,22 +6315,22 @@
         <v>129</v>
       </c>
       <c r="B36" s="4">
-        <v>59777</v>
+        <v>60397</v>
       </c>
       <c r="C36" s="4">
-        <v>62292</v>
+        <v>63040</v>
       </c>
       <c r="D36" s="4">
-        <v>67107</v>
+        <v>68101</v>
       </c>
       <c r="E36" s="4">
-        <v>89727</v>
+        <v>91876</v>
       </c>
       <c r="F36" s="4">
-        <v>63758</v>
+        <v>64580</v>
       </c>
       <c r="G36" s="4">
-        <v>110187</v>
+        <v>113381</v>
       </c>
     </row>
     <row r="37" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6321,22 +6338,22 @@
         <v>130</v>
       </c>
       <c r="B37" s="4">
-        <v>64007</v>
+        <v>64729</v>
       </c>
       <c r="C37" s="4">
-        <v>66939</v>
+        <v>67811</v>
       </c>
       <c r="D37" s="4">
-        <v>72579</v>
+        <v>73739</v>
       </c>
       <c r="E37" s="4">
-        <v>98986</v>
+        <v>101495</v>
       </c>
       <c r="F37" s="4">
-        <v>68639</v>
+        <v>69598</v>
       </c>
       <c r="G37" s="4">
-        <v>122797</v>
+        <v>126522</v>
       </c>
     </row>
     <row r="38" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6344,22 +6361,22 @@
         <v>131</v>
       </c>
       <c r="B38" s="4">
-        <v>68237</v>
+        <v>69062</v>
       </c>
       <c r="C38" s="4">
-        <v>71586</v>
+        <v>72582</v>
       </c>
       <c r="D38" s="4">
-        <v>78050</v>
+        <v>79377</v>
       </c>
       <c r="E38" s="4">
-        <v>108244</v>
+        <v>111113</v>
       </c>
       <c r="F38" s="4">
-        <v>73520</v>
+        <v>74615</v>
       </c>
       <c r="G38" s="4">
-        <v>135406</v>
+        <v>139663</v>
       </c>
     </row>
     <row r="39" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6367,22 +6384,22 @@
         <v>132</v>
       </c>
       <c r="B39" s="4">
-        <v>72466</v>
+        <v>73395</v>
       </c>
       <c r="C39" s="4">
-        <v>76233</v>
+        <v>77354</v>
       </c>
       <c r="D39" s="4">
-        <v>83522</v>
+        <v>85015</v>
       </c>
       <c r="E39" s="4">
-        <v>117503</v>
+        <v>120731</v>
       </c>
       <c r="F39" s="4">
-        <v>78401</v>
+        <v>79633</v>
       </c>
       <c r="G39" s="4">
-        <v>148016</v>
+        <v>152803</v>
       </c>
     </row>
     <row r="40" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6390,22 +6407,22 @@
         <v>133</v>
       </c>
       <c r="B40" s="4">
-        <v>50147</v>
+        <v>50501</v>
       </c>
       <c r="C40" s="4">
-        <v>51613</v>
+        <v>52042</v>
       </c>
       <c r="D40" s="4">
-        <v>54291</v>
+        <v>54856</v>
       </c>
       <c r="E40" s="4">
-        <v>67158</v>
+        <v>68381</v>
       </c>
       <c r="F40" s="4">
-        <v>52489</v>
+        <v>52962</v>
       </c>
       <c r="G40" s="4">
-        <v>79055</v>
+        <v>80885</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6413,22 +6430,22 @@
         <v>134</v>
       </c>
       <c r="B41" s="4">
-        <v>54672</v>
+        <v>55144</v>
       </c>
       <c r="C41" s="4">
-        <v>56606</v>
+        <v>57177</v>
       </c>
       <c r="D41" s="4">
-        <v>60231</v>
+        <v>60986</v>
       </c>
       <c r="E41" s="4">
-        <v>77302</v>
+        <v>78930</v>
       </c>
       <c r="F41" s="4">
-        <v>57747</v>
+        <v>58375</v>
       </c>
       <c r="G41" s="4">
-        <v>93142</v>
+        <v>95579</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6436,22 +6453,22 @@
         <v>135</v>
       </c>
       <c r="B42" s="4">
-        <v>59197</v>
+        <v>59787</v>
       </c>
       <c r="C42" s="4">
-        <v>61600</v>
+        <v>62312</v>
       </c>
       <c r="D42" s="4">
-        <v>66170</v>
+        <v>67116</v>
       </c>
       <c r="E42" s="4">
-        <v>87752</v>
+        <v>89800</v>
       </c>
       <c r="F42" s="4">
-        <v>63004</v>
+        <v>63789</v>
       </c>
       <c r="G42" s="4">
-        <v>107230</v>
+        <v>110274</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6459,22 +6476,22 @@
         <v>136</v>
       </c>
       <c r="B43" s="4">
-        <v>63722</v>
+        <v>64430</v>
       </c>
       <c r="C43" s="4">
-        <v>66593</v>
+        <v>67447</v>
       </c>
       <c r="D43" s="4">
-        <v>72110</v>
+        <v>73247</v>
       </c>
       <c r="E43" s="4">
-        <v>97998</v>
+        <v>100457</v>
       </c>
       <c r="F43" s="4">
-        <v>68262</v>
+        <v>69202</v>
       </c>
       <c r="G43" s="4">
-        <v>121318</v>
+        <v>124968</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6482,22 +6499,22 @@
         <v>137</v>
       </c>
       <c r="B44" s="4">
-        <v>68237</v>
+        <v>69062</v>
       </c>
       <c r="C44" s="4">
-        <v>71586</v>
+        <v>72582</v>
       </c>
       <c r="D44" s="4">
-        <v>78050</v>
+        <v>79377</v>
       </c>
       <c r="E44" s="4">
-        <v>108244</v>
+        <v>111113</v>
       </c>
       <c r="F44" s="4">
-        <v>73520</v>
+        <v>74615</v>
       </c>
       <c r="G44" s="4">
-        <v>135406</v>
+        <v>139663</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6505,22 +6522,22 @@
         <v>138</v>
       </c>
       <c r="B45" s="4">
-        <v>72762</v>
+        <v>73705</v>
       </c>
       <c r="C45" s="4">
-        <v>76579</v>
+        <v>77717</v>
       </c>
       <c r="D45" s="4">
-        <v>83990</v>
+        <v>85507</v>
       </c>
       <c r="E45" s="4">
-        <v>118490</v>
+        <v>121769</v>
       </c>
       <c r="F45" s="4">
-        <v>78778</v>
+        <v>80029</v>
       </c>
       <c r="G45" s="4">
-        <v>149494</v>
+        <v>154357</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6528,22 +6545,22 @@
         <v>139</v>
       </c>
       <c r="B46" s="4">
-        <v>77292</v>
+        <v>78354</v>
       </c>
       <c r="C46" s="4">
-        <v>81578</v>
+        <v>82858</v>
       </c>
       <c r="D46" s="4">
-        <v>89926</v>
+        <v>91632</v>
       </c>
       <c r="E46" s="4">
-        <v>128742</v>
+        <v>132432</v>
       </c>
       <c r="F46" s="4">
-        <v>84042</v>
+        <v>85448</v>
       </c>
       <c r="G46" s="4">
-        <v>163588</v>
+        <v>169058</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6551,22 +6568,22 @@
         <v>140</v>
       </c>
       <c r="B47" s="4">
-        <v>53227</v>
+        <v>53625</v>
       </c>
       <c r="C47" s="4">
-        <v>54876</v>
+        <v>55358</v>
       </c>
       <c r="D47" s="4">
-        <v>57889</v>
+        <v>58525</v>
       </c>
       <c r="E47" s="4">
-        <v>72365</v>
+        <v>73741</v>
       </c>
       <c r="F47" s="4">
-        <v>55863</v>
+        <v>56396</v>
       </c>
       <c r="G47" s="4">
-        <v>85752</v>
+        <v>87811</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6574,22 +6591,22 @@
         <v>141</v>
       </c>
       <c r="B48" s="4">
-        <v>58037</v>
+        <v>58567</v>
       </c>
       <c r="C48" s="4">
-        <v>60215</v>
+        <v>60857</v>
       </c>
       <c r="D48" s="4">
-        <v>64297</v>
+        <v>65148</v>
       </c>
       <c r="E48" s="4">
-        <v>83497</v>
+        <v>85328</v>
       </c>
       <c r="F48" s="4">
-        <v>61498</v>
+        <v>62205</v>
       </c>
       <c r="G48" s="4">
-        <v>101318</v>
+        <v>104059</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6597,22 +6614,22 @@
         <v>142</v>
       </c>
       <c r="B49" s="4">
-        <v>62857</v>
+        <v>63520</v>
       </c>
       <c r="C49" s="4">
-        <v>65554</v>
+        <v>66356</v>
       </c>
       <c r="D49" s="4">
-        <v>70705</v>
+        <v>71770</v>
       </c>
       <c r="E49" s="4">
-        <v>95036</v>
+        <v>97343</v>
       </c>
       <c r="F49" s="4">
-        <v>67132</v>
+        <v>68014</v>
       </c>
       <c r="G49" s="4">
-        <v>116884</v>
+        <v>120307</v>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6620,22 +6637,22 @@
         <v>143</v>
       </c>
       <c r="B50" s="4">
-        <v>67667</v>
+        <v>68463</v>
       </c>
       <c r="C50" s="4">
-        <v>70894</v>
+        <v>71855</v>
       </c>
       <c r="D50" s="4">
-        <v>77114</v>
+        <v>78392</v>
       </c>
       <c r="E50" s="4">
-        <v>106269</v>
+        <v>109037</v>
       </c>
       <c r="F50" s="4">
-        <v>72767</v>
+        <v>73823</v>
       </c>
       <c r="G50" s="4">
-        <v>132450</v>
+        <v>136555</v>
       </c>
     </row>
     <row r="51" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6643,22 +6660,22 @@
         <v>144</v>
       </c>
       <c r="B51" s="4">
-        <v>72466</v>
+        <v>73395</v>
       </c>
       <c r="C51" s="4">
-        <v>76233</v>
+        <v>77354</v>
       </c>
       <c r="D51" s="4">
-        <v>83522</v>
+        <v>85015</v>
       </c>
       <c r="E51" s="4">
-        <v>117503</v>
+        <v>120731</v>
       </c>
       <c r="F51" s="4">
-        <v>78401</v>
+        <v>79633</v>
       </c>
       <c r="G51" s="4">
-        <v>148016</v>
+        <v>152803</v>
       </c>
     </row>
     <row r="52" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6666,22 +6683,22 @@
         <v>145</v>
       </c>
       <c r="B52" s="4">
-        <v>77292</v>
+        <v>78354</v>
       </c>
       <c r="C52" s="4">
-        <v>81578</v>
+        <v>82858</v>
       </c>
       <c r="D52" s="4">
-        <v>89926</v>
+        <v>91632</v>
       </c>
       <c r="E52" s="4">
-        <v>128742</v>
+        <v>132432</v>
       </c>
       <c r="F52" s="4">
-        <v>84042</v>
+        <v>85448</v>
       </c>
       <c r="G52" s="4">
-        <v>163588</v>
+        <v>169058</v>
       </c>
     </row>
     <row r="53" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6689,22 +6706,22 @@
         <v>25</v>
       </c>
       <c r="B53" s="4">
-        <v>82112</v>
+        <v>83307</v>
       </c>
       <c r="C53" s="4">
-        <v>86388</v>
+        <v>87801</v>
       </c>
       <c r="D53" s="4">
-        <v>96324</v>
+        <v>98244</v>
       </c>
       <c r="E53" s="4">
-        <v>139436</v>
+        <v>143559</v>
       </c>
       <c r="F53" s="4">
-        <v>89676</v>
+        <v>91257</v>
       </c>
       <c r="G53" s="4">
-        <v>179154</v>
+        <v>185306</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6712,22 +6729,22 @@
         <v>146</v>
       </c>
       <c r="B54" s="4">
-        <v>56306</v>
+        <v>56748</v>
       </c>
       <c r="C54" s="4">
-        <v>58138</v>
+        <v>58674</v>
       </c>
       <c r="D54" s="4">
-        <v>61498</v>
+        <v>62205</v>
       </c>
       <c r="E54" s="4">
-        <v>77541</v>
+        <v>79068</v>
       </c>
       <c r="F54" s="4">
-        <v>59197</v>
+        <v>59787</v>
       </c>
       <c r="G54" s="4">
-        <v>92376</v>
+        <v>94660</v>
       </c>
     </row>
     <row r="55" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6735,22 +6752,22 @@
         <v>147</v>
       </c>
       <c r="B55" s="4">
-        <v>61411</v>
+        <v>62001</v>
       </c>
       <c r="C55" s="4">
-        <v>63844</v>
+        <v>64558</v>
       </c>
       <c r="D55" s="4">
-        <v>68323</v>
+        <v>69266</v>
       </c>
       <c r="E55" s="4">
-        <v>89722</v>
+        <v>91758</v>
       </c>
       <c r="F55" s="4">
-        <v>65259</v>
+        <v>66045</v>
       </c>
       <c r="G55" s="4">
-        <v>109506</v>
+        <v>112552</v>
       </c>
     </row>
     <row r="56" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6758,22 +6775,22 @@
         <v>148</v>
       </c>
       <c r="B56" s="4">
-        <v>66516</v>
+        <v>67254</v>
       </c>
       <c r="C56" s="4">
-        <v>69560</v>
+        <v>70453</v>
       </c>
       <c r="D56" s="4">
-        <v>75149</v>
+        <v>76327</v>
       </c>
       <c r="E56" s="4">
-        <v>101902</v>
+        <v>104447</v>
       </c>
       <c r="F56" s="4">
-        <v>71321</v>
+        <v>72304</v>
       </c>
       <c r="G56" s="4">
-        <v>126635</v>
+        <v>130444</v>
       </c>
     </row>
     <row r="57" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6781,22 +6798,22 @@
         <v>149</v>
       </c>
       <c r="B57" s="4">
-        <v>71621</v>
+        <v>72506</v>
       </c>
       <c r="C57" s="4">
-        <v>75266</v>
+        <v>76337</v>
       </c>
       <c r="D57" s="4">
-        <v>81974</v>
+        <v>83388</v>
       </c>
       <c r="E57" s="4">
-        <v>114082</v>
+        <v>117136</v>
       </c>
       <c r="F57" s="4">
-        <v>77383</v>
+        <v>78563</v>
       </c>
       <c r="G57" s="4">
-        <v>143765</v>
+        <v>148335</v>
       </c>
     </row>
     <row r="58" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6804,22 +6821,22 @@
         <v>150</v>
       </c>
       <c r="B58" s="4">
-        <v>76732</v>
+        <v>77765</v>
       </c>
       <c r="C58" s="4">
-        <v>80978</v>
+        <v>82227</v>
       </c>
       <c r="D58" s="4">
-        <v>88806</v>
+        <v>90455</v>
       </c>
       <c r="E58" s="4">
-        <v>126268</v>
+        <v>129831</v>
       </c>
       <c r="F58" s="4">
-        <v>83451</v>
+        <v>84827</v>
       </c>
       <c r="G58" s="4">
-        <v>160901</v>
+        <v>166233</v>
       </c>
     </row>
     <row r="59" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6827,22 +6844,22 @@
         <v>151</v>
       </c>
       <c r="B59" s="4">
-        <v>81838</v>
+        <v>83018</v>
       </c>
       <c r="C59" s="4">
-        <v>86683</v>
+        <v>88111</v>
       </c>
       <c r="D59" s="4">
-        <v>95632</v>
+        <v>97517</v>
       </c>
       <c r="E59" s="4">
-        <v>138449</v>
+        <v>142521</v>
       </c>
       <c r="F59" s="4">
-        <v>89513</v>
+        <v>91086</v>
       </c>
       <c r="G59" s="4">
-        <v>178030</v>
+        <v>184124</v>
       </c>
     </row>
     <row r="60" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6850,22 +6867,22 @@
         <v>32</v>
       </c>
       <c r="B60" s="4">
-        <v>86943</v>
+        <v>88271</v>
       </c>
       <c r="C60" s="4">
-        <v>92389</v>
+        <v>93995</v>
       </c>
       <c r="D60" s="4">
-        <v>102457</v>
+        <v>104578</v>
       </c>
       <c r="E60" s="4">
-        <v>150629</v>
+        <v>155210</v>
       </c>
       <c r="F60" s="4">
-        <v>95575</v>
+        <v>97344</v>
       </c>
       <c r="G60" s="4">
-        <v>195160</v>
+        <v>202016</v>
       </c>
     </row>
     <row r="61" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6873,22 +6890,22 @@
         <v>152</v>
       </c>
       <c r="B61" s="4">
-        <v>59395</v>
+        <v>59882</v>
       </c>
       <c r="C61" s="4">
-        <v>61401</v>
+        <v>61990</v>
       </c>
       <c r="D61" s="4">
-        <v>65096</v>
+        <v>65874</v>
       </c>
       <c r="E61" s="4">
-        <v>82748</v>
+        <v>84428</v>
       </c>
       <c r="F61" s="4">
-        <v>62561</v>
+        <v>63210</v>
       </c>
       <c r="G61" s="4">
-        <v>99061</v>
+        <v>101574</v>
       </c>
     </row>
     <row r="62" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6896,22 +6913,22 @@
         <v>153</v>
       </c>
       <c r="B62" s="4">
-        <v>64786</v>
+        <v>65435</v>
       </c>
       <c r="C62" s="4">
-        <v>67463</v>
+        <v>68249</v>
       </c>
       <c r="D62" s="4">
-        <v>72390</v>
+        <v>73428</v>
       </c>
       <c r="E62" s="4">
-        <v>95926</v>
+        <v>98166</v>
       </c>
       <c r="F62" s="4">
-        <v>69010</v>
+        <v>69875</v>
       </c>
       <c r="G62" s="4">
-        <v>117681</v>
+        <v>121032</v>
       </c>
     </row>
     <row r="63" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6919,22 +6936,22 @@
         <v>154</v>
       </c>
       <c r="B63" s="4">
-        <v>70176</v>
+        <v>70987</v>
       </c>
       <c r="C63" s="4">
-        <v>73525</v>
+        <v>74507</v>
       </c>
       <c r="D63" s="4">
-        <v>79684</v>
+        <v>80981</v>
       </c>
       <c r="E63" s="4">
-        <v>109104</v>
+        <v>111904</v>
       </c>
       <c r="F63" s="4">
-        <v>75459</v>
+        <v>76540</v>
       </c>
       <c r="G63" s="4">
-        <v>136301</v>
+        <v>140490</v>
       </c>
     </row>
     <row r="64" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6942,22 +6959,22 @@
         <v>155</v>
       </c>
       <c r="B64" s="4">
-        <v>75572</v>
+        <v>76545</v>
       </c>
       <c r="C64" s="4">
-        <v>79593</v>
+        <v>80772</v>
       </c>
       <c r="D64" s="4">
-        <v>86984</v>
+        <v>88540</v>
       </c>
       <c r="E64" s="4">
-        <v>122288</v>
+        <v>125648</v>
       </c>
       <c r="F64" s="4">
-        <v>81914</v>
+        <v>83212</v>
       </c>
       <c r="G64" s="4">
-        <v>154927</v>
+        <v>159954</v>
       </c>
     </row>
     <row r="65" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6965,22 +6982,22 @@
         <v>156</v>
       </c>
       <c r="B65" s="4">
-        <v>80962</v>
+        <v>82098</v>
       </c>
       <c r="C65" s="4">
-        <v>85655</v>
+        <v>87031</v>
       </c>
       <c r="D65" s="4">
-        <v>94278</v>
+        <v>96093</v>
       </c>
       <c r="E65" s="4">
-        <v>135466</v>
+        <v>139386</v>
       </c>
       <c r="F65" s="4">
-        <v>88363</v>
+        <v>89877</v>
       </c>
       <c r="G65" s="4">
-        <v>173547</v>
+        <v>179412</v>
       </c>
     </row>
     <row r="66" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6988,22 +7005,22 @@
         <v>157</v>
       </c>
       <c r="B66" s="4">
-        <v>86352</v>
+        <v>87650</v>
       </c>
       <c r="C66" s="4">
-        <v>91717</v>
+        <v>93289</v>
       </c>
       <c r="D66" s="4">
-        <v>101571</v>
+        <v>103647</v>
       </c>
       <c r="E66" s="4">
-        <v>148644</v>
+        <v>153124</v>
       </c>
       <c r="F66" s="4">
-        <v>94812</v>
+        <v>96542</v>
       </c>
       <c r="G66" s="4">
-        <v>192167</v>
+        <v>198870</v>
       </c>
     </row>
     <row r="67" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7011,22 +7028,22 @@
         <v>38</v>
       </c>
       <c r="B67" s="4">
-        <v>91743</v>
+        <v>93204</v>
       </c>
       <c r="C67" s="4">
-        <v>97780</v>
+        <v>99549</v>
       </c>
       <c r="D67" s="4">
-        <v>108866</v>
+        <v>111201</v>
       </c>
       <c r="E67" s="4">
-        <v>161823</v>
+        <v>166862</v>
       </c>
       <c r="F67" s="4">
-        <v>101262</v>
+        <v>103208</v>
       </c>
       <c r="G67" s="4">
-        <v>210788</v>
+        <v>218329</v>
       </c>
     </row>
     <row r="68" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7034,22 +7051,22 @@
         <v>158</v>
       </c>
       <c r="B68" s="4">
-        <v>68639</v>
+        <v>69259</v>
       </c>
       <c r="C68" s="4">
-        <v>71195</v>
+        <v>71944</v>
       </c>
       <c r="D68" s="4">
-        <v>75898</v>
+        <v>76888</v>
       </c>
       <c r="E68" s="4">
-        <v>98365</v>
+        <v>100503</v>
       </c>
       <c r="F68" s="4">
-        <v>72681</v>
+        <v>73507</v>
       </c>
       <c r="G68" s="4">
-        <v>119134</v>
+        <v>122333</v>
       </c>
     </row>
     <row r="69" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7057,22 +7074,22 @@
         <v>159</v>
       </c>
       <c r="B69" s="4">
-        <v>74895</v>
+        <v>75721</v>
       </c>
       <c r="C69" s="4">
-        <v>78305</v>
+        <v>79305</v>
       </c>
       <c r="D69" s="4">
-        <v>84576</v>
+        <v>85896</v>
       </c>
       <c r="E69" s="4">
-        <v>114526</v>
+        <v>117376</v>
       </c>
       <c r="F69" s="4">
-        <v>80280</v>
+        <v>81381</v>
       </c>
       <c r="G69" s="4">
-        <v>142213</v>
+        <v>146478</v>
       </c>
     </row>
     <row r="70" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7080,22 +7097,22 @@
         <v>160</v>
       </c>
       <c r="B70" s="4">
-        <v>81150</v>
+        <v>82183</v>
       </c>
       <c r="C70" s="4">
-        <v>85416</v>
+        <v>86666</v>
       </c>
       <c r="D70" s="4">
-        <v>93254</v>
+        <v>94905</v>
       </c>
       <c r="E70" s="4">
-        <v>130686</v>
+        <v>134249</v>
       </c>
       <c r="F70" s="4">
-        <v>87879</v>
+        <v>89255</v>
       </c>
       <c r="G70" s="4">
-        <v>165292</v>
+        <v>170622</v>
       </c>
     </row>
     <row r="71" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7103,22 +7120,22 @@
         <v>161</v>
       </c>
       <c r="B71" s="4">
-        <v>87407</v>
+        <v>88645</v>
       </c>
       <c r="C71" s="4">
-        <v>92527</v>
+        <v>94028</v>
       </c>
       <c r="D71" s="4">
-        <v>101934</v>
+        <v>103914</v>
       </c>
       <c r="E71" s="4">
-        <v>146848</v>
+        <v>151123</v>
       </c>
       <c r="F71" s="4">
-        <v>95480</v>
+        <v>97131</v>
       </c>
       <c r="G71" s="4">
-        <v>188372</v>
+        <v>194768</v>
       </c>
     </row>
     <row r="72" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7126,22 +7143,22 @@
         <v>162</v>
       </c>
       <c r="B72" s="4">
-        <v>93662</v>
+        <v>95107</v>
       </c>
       <c r="C72" s="4">
-        <v>99638</v>
+        <v>101388</v>
       </c>
       <c r="D72" s="4">
-        <v>110612</v>
+        <v>112923</v>
       </c>
       <c r="E72" s="4">
-        <v>163008</v>
+        <v>167996</v>
       </c>
       <c r="F72" s="4">
-        <v>103079</v>
+        <v>105005</v>
       </c>
       <c r="G72" s="4">
-        <v>203755</v>
+        <v>210824</v>
       </c>
     </row>
     <row r="73" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7149,22 +7166,22 @@
         <v>163</v>
       </c>
       <c r="B73" s="4">
-        <v>99918</v>
+        <v>101569</v>
       </c>
       <c r="C73" s="4">
-        <v>106748</v>
+        <v>108749</v>
       </c>
       <c r="D73" s="4">
-        <v>119290</v>
+        <v>121931</v>
       </c>
       <c r="E73" s="4">
-        <v>179169</v>
+        <v>184869</v>
       </c>
       <c r="F73" s="4">
-        <v>110678</v>
+        <v>112879</v>
       </c>
       <c r="G73" s="4">
-        <v>219138</v>
+        <v>226879</v>
       </c>
     </row>
     <row r="74" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7172,22 +7189,22 @@
         <v>45</v>
       </c>
       <c r="B74" s="4">
-        <v>106173</v>
+        <v>108031</v>
       </c>
       <c r="C74" s="4">
-        <v>113859</v>
+        <v>116110</v>
       </c>
       <c r="D74" s="4">
-        <v>127969</v>
+        <v>130940</v>
       </c>
       <c r="E74" s="4">
-        <v>195330</v>
+        <v>201742</v>
       </c>
       <c r="F74" s="4">
-        <v>118277</v>
+        <v>120753</v>
       </c>
       <c r="G74" s="4">
-        <v>242217</v>
+        <v>251024</v>
       </c>
     </row>
   </sheetData>
@@ -7260,19 +7277,19 @@
         <v>169</v>
       </c>
       <c r="C6" s="4">
-        <v>152343</v>
+        <v>153753</v>
       </c>
       <c r="D6" s="4">
-        <v>160894</v>
+        <v>162750</v>
       </c>
       <c r="E6" s="4">
-        <v>155058</v>
+        <v>156609</v>
       </c>
       <c r="F6" s="4">
-        <v>202241</v>
+        <v>206257</v>
       </c>
       <c r="G6" s="4">
-        <v>240402</v>
+        <v>246412</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7283,16 +7300,16 @@
         <v>169</v>
       </c>
       <c r="C7" s="4">
-        <v>193131</v>
+        <v>194541</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>169</v>
       </c>
       <c r="E7" s="4">
-        <v>195846</v>
+        <v>197397</v>
       </c>
       <c r="F7" s="4">
-        <v>243029</v>
+        <v>247045</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>169</v>
@@ -7303,19 +7320,19 @@
         <v>171</v>
       </c>
       <c r="B8" s="4">
-        <v>153224</v>
+        <v>154326</v>
       </c>
       <c r="C8" s="4">
-        <v>157703</v>
+        <v>159039</v>
       </c>
       <c r="D8" s="4">
-        <v>165792</v>
+        <v>167550</v>
       </c>
       <c r="E8" s="4">
-        <v>160266</v>
+        <v>161736</v>
       </c>
       <c r="F8" s="4">
-        <v>204968</v>
+        <v>208774</v>
       </c>
       <c r="G8" s="4">
         <v>215175</v>
@@ -7326,19 +7343,19 @@
         <v>172</v>
       </c>
       <c r="B9" s="4">
-        <v>185359</v>
+        <v>185910</v>
       </c>
       <c r="C9" s="4">
-        <v>187598</v>
+        <v>188266</v>
       </c>
       <c r="D9" s="4">
-        <v>191642</v>
+        <v>192522</v>
       </c>
       <c r="E9" s="4">
-        <v>188879</v>
+        <v>189614</v>
       </c>
       <c r="F9" s="4">
-        <v>211231</v>
+        <v>213133</v>
       </c>
       <c r="G9" s="4">
         <v>216334</v>
@@ -7349,7 +7366,7 @@
         <v>173</v>
       </c>
       <c r="B10" s="4">
-        <v>210632</v>
+        <v>211183</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>169</v>
@@ -7358,10 +7375,10 @@
         <v>169</v>
       </c>
       <c r="E10" s="4">
-        <v>214152</v>
+        <v>214887</v>
       </c>
       <c r="F10" s="4">
-        <v>236504</v>
+        <v>238406</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>169</v>
@@ -7372,19 +7389,19 @@
         <v>174</v>
       </c>
       <c r="B11" s="4">
-        <v>202047</v>
+        <v>202355</v>
       </c>
       <c r="C11" s="4">
-        <v>203253</v>
+        <v>203624</v>
       </c>
       <c r="D11" s="4">
-        <v>205506</v>
+        <v>205994</v>
       </c>
       <c r="E11" s="4">
-        <v>203969</v>
+        <v>204378</v>
       </c>
       <c r="F11" s="4">
-        <v>216385</v>
+        <v>217442</v>
       </c>
       <c r="G11" s="4">
         <v>219220</v>
@@ -7395,7 +7412,7 @@
         <v>175</v>
       </c>
       <c r="B12" s="4">
-        <v>218836</v>
+        <v>219144</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>169</v>
@@ -7404,10 +7421,10 @@
         <v>169</v>
       </c>
       <c r="E12" s="4">
-        <v>220758</v>
+        <v>221167</v>
       </c>
       <c r="F12" s="4">
-        <v>233174</v>
+        <v>234231</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>169</v>
@@ -7441,19 +7458,19 @@
         <v>177</v>
       </c>
       <c r="B14" s="4">
-        <v>205575</v>
+        <v>206126</v>
       </c>
       <c r="C14" s="4">
-        <v>207814</v>
+        <v>208482</v>
       </c>
       <c r="D14" s="4">
-        <v>211858</v>
+        <v>212738</v>
       </c>
       <c r="E14" s="4">
-        <v>209095</v>
+        <v>209830</v>
       </c>
       <c r="F14" s="4">
-        <v>231447</v>
+        <v>233349</v>
       </c>
       <c r="G14" s="4">
         <v>236550</v>
@@ -7464,19 +7481,19 @@
         <v>178</v>
       </c>
       <c r="B15" s="4">
-        <v>212154</v>
+        <v>212462</v>
       </c>
       <c r="C15" s="4">
-        <v>213360</v>
+        <v>213731</v>
       </c>
       <c r="D15" s="4">
-        <v>215613</v>
+        <v>216101</v>
       </c>
       <c r="E15" s="4">
-        <v>214076</v>
+        <v>214485</v>
       </c>
       <c r="F15" s="4">
-        <v>226492</v>
+        <v>227549</v>
       </c>
       <c r="G15" s="4">
         <v>229327</v>
@@ -7487,19 +7504,19 @@
         <v>179</v>
       </c>
       <c r="B16" s="4">
-        <v>171428</v>
+        <v>172659</v>
       </c>
       <c r="C16" s="4">
-        <v>176251</v>
+        <v>177734</v>
       </c>
       <c r="D16" s="4">
-        <v>185263</v>
+        <v>187217</v>
       </c>
       <c r="E16" s="4">
-        <v>179117</v>
+        <v>180750</v>
       </c>
       <c r="F16" s="4">
-        <v>228780</v>
+        <v>233008</v>
       </c>
       <c r="G16" s="4">
         <v>240121</v>
@@ -7510,19 +7527,19 @@
         <v>180</v>
       </c>
       <c r="B17" s="4">
-        <v>206946</v>
+        <v>207333</v>
       </c>
       <c r="C17" s="4">
-        <v>208516</v>
+        <v>208986</v>
       </c>
       <c r="D17" s="4">
-        <v>211369</v>
+        <v>211988</v>
       </c>
       <c r="E17" s="4">
-        <v>209447</v>
+        <v>209965</v>
       </c>
       <c r="F17" s="4">
-        <v>225156</v>
+        <v>226495</v>
       </c>
       <c r="G17" s="4">
         <v>228744</v>
@@ -7533,19 +7550,19 @@
         <v>181</v>
       </c>
       <c r="B18" s="4">
-        <v>215978</v>
+        <v>216192</v>
       </c>
       <c r="C18" s="4">
-        <v>217555</v>
+        <v>217852</v>
       </c>
       <c r="D18" s="4">
-        <v>219354</v>
+        <v>219744</v>
       </c>
       <c r="E18" s="4">
-        <v>218127</v>
+        <v>218454</v>
       </c>
       <c r="F18" s="4">
-        <v>228063</v>
+        <v>228908</v>
       </c>
       <c r="G18" s="4">
         <v>230324</v>
@@ -7556,7 +7573,7 @@
         <v>182</v>
       </c>
       <c r="B19" s="4">
-        <v>232540</v>
+        <v>232754</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>169</v>
@@ -7565,10 +7582,10 @@
         <v>169</v>
       </c>
       <c r="E19" s="4">
-        <v>234689</v>
+        <v>235016</v>
       </c>
       <c r="F19" s="4">
-        <v>244625</v>
+        <v>245470</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>169</v>
@@ -7579,19 +7596,19 @@
         <v>183</v>
       </c>
       <c r="B20" s="4">
-        <v>201329</v>
+        <v>202186</v>
       </c>
       <c r="C20" s="4">
-        <v>206214</v>
+        <v>207327</v>
       </c>
       <c r="D20" s="4">
-        <v>212966</v>
+        <v>214432</v>
       </c>
       <c r="E20" s="4">
-        <v>208364</v>
+        <v>209589</v>
       </c>
       <c r="F20" s="4">
-        <v>245618</v>
+        <v>248789</v>
       </c>
       <c r="G20" s="4">
         <v>254123</v>
@@ -7602,19 +7619,19 @@
         <v>184</v>
       </c>
       <c r="B21" s="4">
-        <v>169884</v>
+        <v>170741</v>
       </c>
       <c r="C21" s="4">
-        <v>174769</v>
+        <v>175882</v>
       </c>
       <c r="D21" s="4">
-        <v>181521</v>
+        <v>182987</v>
       </c>
       <c r="E21" s="4">
-        <v>176919</v>
+        <v>178144</v>
       </c>
       <c r="F21" s="4">
-        <v>214173</v>
+        <v>217344</v>
       </c>
       <c r="G21" s="4">
         <v>222678</v>
@@ -7702,16 +7719,16 @@
         <v>190</v>
       </c>
       <c r="B6" s="4">
-        <v>120807</v>
+        <v>121721</v>
       </c>
       <c r="C6" s="4">
-        <v>179819</v>
+        <v>183725</v>
       </c>
       <c r="D6" s="4">
-        <v>122622</v>
+        <v>123627</v>
       </c>
       <c r="E6" s="4">
-        <v>154127</v>
+        <v>156731</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7719,16 +7736,16 @@
         <v>191</v>
       </c>
       <c r="B7" s="4">
-        <v>135659</v>
+        <v>136573</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>169</v>
       </c>
       <c r="D7" s="4">
-        <v>137474</v>
+        <v>138479</v>
       </c>
       <c r="E7" s="4">
-        <v>168979</v>
+        <v>171583</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7736,16 +7753,16 @@
         <v>192</v>
       </c>
       <c r="B8" s="4">
-        <v>142121</v>
+        <v>142842</v>
       </c>
       <c r="C8" s="4">
-        <v>188715</v>
+        <v>191800</v>
       </c>
       <c r="D8" s="4">
-        <v>143556</v>
+        <v>144350</v>
       </c>
       <c r="E8" s="4">
-        <v>168431</v>
+        <v>170486</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7753,16 +7770,16 @@
         <v>193</v>
       </c>
       <c r="B9" s="4">
-        <v>157084</v>
+        <v>157805</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>169</v>
       </c>
       <c r="D9" s="4">
-        <v>158519</v>
+        <v>159313</v>
       </c>
       <c r="E9" s="4">
-        <v>183394</v>
+        <v>185449</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7770,16 +7787,16 @@
         <v>194</v>
       </c>
       <c r="B10" s="4">
-        <v>164643</v>
+        <v>165124</v>
       </c>
       <c r="C10" s="4">
-        <v>195701</v>
+        <v>197757</v>
       </c>
       <c r="D10" s="4">
-        <v>165595</v>
+        <v>166124</v>
       </c>
       <c r="E10" s="4">
-        <v>182176</v>
+        <v>183546</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7787,16 +7804,16 @@
         <v>195</v>
       </c>
       <c r="B11" s="4">
-        <v>172761</v>
+        <v>173242</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>169</v>
       </c>
       <c r="D11" s="4">
-        <v>173713</v>
+        <v>174242</v>
       </c>
       <c r="E11" s="4">
-        <v>190294</v>
+        <v>191664</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7804,16 +7821,16 @@
         <v>196</v>
       </c>
       <c r="B12" s="4">
-        <v>147273</v>
+        <v>148475</v>
       </c>
       <c r="C12" s="4">
-        <v>224925</v>
+        <v>230066</v>
       </c>
       <c r="D12" s="4">
-        <v>149660</v>
+        <v>150983</v>
       </c>
       <c r="E12" s="4">
-        <v>191115</v>
+        <v>194541</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7821,16 +7838,16 @@
         <v>197</v>
       </c>
       <c r="B13" s="4">
-        <v>134500</v>
+        <v>146000</v>
       </c>
       <c r="C13" s="4">
-        <v>180000</v>
+        <v>191000</v>
       </c>
       <c r="D13" s="4">
-        <v>134000</v>
+        <v>145000</v>
       </c>
       <c r="E13" s="4">
-        <v>164000</v>
+        <v>176000</v>
       </c>
     </row>
   </sheetData>
@@ -7905,25 +7922,25 @@
         <v>6</v>
       </c>
       <c r="B6" s="4">
-        <v>81803</v>
+        <v>84342</v>
       </c>
       <c r="C6" s="4">
-        <v>82369</v>
+        <v>84938</v>
       </c>
       <c r="D6" s="4">
-        <v>83406</v>
+        <v>86027</v>
       </c>
       <c r="E6" s="4">
-        <v>92595</v>
+        <v>95678</v>
       </c>
       <c r="F6" s="4">
         <v>7179</v>
       </c>
       <c r="G6" s="4">
-        <v>9900</v>
+        <v>10201</v>
       </c>
       <c r="H6" s="4">
-        <v>121762</v>
+        <v>124496</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7931,25 +7948,25 @@
         <v>7</v>
       </c>
       <c r="B7" s="4">
-        <v>90440</v>
+        <v>93263</v>
       </c>
       <c r="C7" s="4">
-        <v>91242</v>
+        <v>94107</v>
       </c>
       <c r="D7" s="4">
-        <v>92698</v>
+        <v>95637</v>
       </c>
       <c r="E7" s="4">
-        <v>105565</v>
+        <v>109151</v>
       </c>
       <c r="F7" s="4">
         <v>7179</v>
       </c>
       <c r="G7" s="4">
-        <v>11600</v>
+        <v>11953</v>
       </c>
       <c r="H7" s="4">
-        <v>137106</v>
+        <v>140201</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7957,25 +7974,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="4">
-        <v>100259</v>
+        <v>103400</v>
       </c>
       <c r="C8" s="4">
-        <v>101296</v>
+        <v>104493</v>
       </c>
       <c r="D8" s="4">
-        <v>103160</v>
+        <v>106450</v>
       </c>
       <c r="E8" s="4">
-        <v>119703</v>
+        <v>123826</v>
       </c>
       <c r="F8" s="4">
         <v>7179</v>
       </c>
       <c r="G8" s="4">
-        <v>13300</v>
+        <v>13704</v>
       </c>
       <c r="H8" s="4">
-        <v>153635</v>
+        <v>157129</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7983,25 +8000,25 @@
         <v>9</v>
       </c>
       <c r="B9" s="4">
-        <v>110097</v>
+        <v>113557</v>
       </c>
       <c r="C9" s="4">
-        <v>111350</v>
+        <v>114878</v>
       </c>
       <c r="D9" s="4">
-        <v>113633</v>
+        <v>117276</v>
       </c>
       <c r="E9" s="4">
-        <v>133848</v>
+        <v>138507</v>
       </c>
       <c r="F9" s="4">
         <v>7179</v>
       </c>
       <c r="G9" s="4">
-        <v>15000</v>
+        <v>15456</v>
       </c>
       <c r="H9" s="4">
-        <v>170159</v>
+        <v>174050</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8009,25 +8026,25 @@
         <v>10</v>
       </c>
       <c r="B10" s="4">
-        <v>126587</v>
+        <v>130580</v>
       </c>
       <c r="C10" s="4">
-        <v>128190</v>
+        <v>132270</v>
       </c>
       <c r="D10" s="4">
-        <v>131097</v>
+        <v>135322</v>
       </c>
       <c r="E10" s="4">
-        <v>156829</v>
+        <v>162350</v>
       </c>
       <c r="F10" s="4">
         <v>7179</v>
       </c>
       <c r="G10" s="4">
-        <v>17550</v>
+        <v>18084</v>
       </c>
       <c r="H10" s="4">
-        <v>196698</v>
+        <v>201240</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8035,25 +8052,25 @@
         <v>11</v>
       </c>
       <c r="B11" s="4">
-        <v>143610</v>
+        <v>148151</v>
       </c>
       <c r="C11" s="4">
-        <v>145549</v>
+        <v>150196</v>
       </c>
       <c r="D11" s="4">
-        <v>149079</v>
+        <v>153903</v>
       </c>
       <c r="E11" s="4">
-        <v>180331</v>
+        <v>186728</v>
       </c>
       <c r="F11" s="4">
         <v>7179</v>
       </c>
       <c r="G11" s="4">
-        <v>20100</v>
+        <v>20711</v>
       </c>
       <c r="H11" s="4">
-        <v>223761</v>
+        <v>228969</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8061,25 +8078,25 @@
         <v>12</v>
       </c>
       <c r="B12" s="4">
-        <v>160016</v>
+        <v>165077</v>
       </c>
       <c r="C12" s="4">
-        <v>162191</v>
+        <v>167369</v>
       </c>
       <c r="D12" s="4">
-        <v>166128</v>
+        <v>171504</v>
       </c>
       <c r="E12" s="4">
-        <v>201064</v>
+        <v>208198</v>
       </c>
       <c r="F12" s="4">
         <v>7179</v>
       </c>
       <c r="G12" s="4">
-        <v>21800</v>
+        <v>22463</v>
       </c>
       <c r="H12" s="4">
-        <v>246880</v>
+        <v>252684</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8087,25 +8104,25 @@
         <v>13</v>
       </c>
       <c r="B13" s="4">
-        <v>93697</v>
+        <v>96632</v>
       </c>
       <c r="C13" s="4">
-        <v>94645</v>
+        <v>97630</v>
       </c>
       <c r="D13" s="4">
-        <v>96381</v>
+        <v>99454</v>
       </c>
       <c r="E13" s="4">
-        <v>111697</v>
+        <v>115541</v>
       </c>
       <c r="F13" s="4">
         <v>10768</v>
       </c>
       <c r="G13" s="4">
-        <v>13050</v>
+        <v>13447</v>
       </c>
       <c r="H13" s="4">
-        <v>146539</v>
+        <v>149798</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8113,25 +8130,25 @@
         <v>14</v>
       </c>
       <c r="B14" s="4">
-        <v>103090</v>
+        <v>106345</v>
       </c>
       <c r="C14" s="4">
-        <v>104426</v>
+        <v>107752</v>
       </c>
       <c r="D14" s="4">
-        <v>106849</v>
+        <v>110297</v>
       </c>
       <c r="E14" s="4">
-        <v>128291</v>
+        <v>132818</v>
       </c>
       <c r="F14" s="4">
         <v>10768</v>
       </c>
       <c r="G14" s="4">
-        <v>15000</v>
+        <v>15456</v>
       </c>
       <c r="H14" s="4">
-        <v>163668</v>
+        <v>167378</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8139,25 +8156,25 @@
         <v>15</v>
       </c>
       <c r="B15" s="4">
-        <v>113734</v>
+        <v>117347</v>
       </c>
       <c r="C15" s="4">
-        <v>115445</v>
+        <v>119151</v>
       </c>
       <c r="D15" s="4">
-        <v>118562</v>
+        <v>122424</v>
       </c>
       <c r="E15" s="4">
-        <v>146137</v>
+        <v>151386</v>
       </c>
       <c r="F15" s="4">
         <v>10768</v>
       </c>
       <c r="G15" s="4">
-        <v>16950</v>
+        <v>17465</v>
       </c>
       <c r="H15" s="4">
-        <v>182028</v>
+        <v>186229</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8165,25 +8182,25 @@
         <v>16</v>
       </c>
       <c r="B16" s="4">
-        <v>124284</v>
+        <v>128252</v>
       </c>
       <c r="C16" s="4">
-        <v>126383</v>
+        <v>130465</v>
       </c>
       <c r="D16" s="4">
-        <v>130186</v>
+        <v>134459</v>
       </c>
       <c r="E16" s="4">
-        <v>163887</v>
+        <v>169856</v>
       </c>
       <c r="F16" s="4">
         <v>10768</v>
       </c>
       <c r="G16" s="4">
-        <v>18900</v>
+        <v>19475</v>
       </c>
       <c r="H16" s="4">
-        <v>200313</v>
+        <v>205000</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8191,25 +8208,25 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>141875</v>
+        <v>146429</v>
       </c>
       <c r="C17" s="4">
-        <v>144539</v>
+        <v>149238</v>
       </c>
       <c r="D17" s="4">
-        <v>149379</v>
+        <v>154321</v>
       </c>
       <c r="E17" s="4">
-        <v>192277</v>
+        <v>199377</v>
       </c>
       <c r="F17" s="4">
         <v>10768</v>
       </c>
       <c r="G17" s="4">
-        <v>21825</v>
+        <v>22488</v>
       </c>
       <c r="H17" s="4">
-        <v>229484</v>
+        <v>234953</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8217,25 +8234,25 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>159466</v>
+        <v>164606</v>
       </c>
       <c r="C18" s="4">
-        <v>162703</v>
+        <v>168018</v>
       </c>
       <c r="D18" s="4">
-        <v>168586</v>
+        <v>174197</v>
       </c>
       <c r="E18" s="4">
-        <v>220666</v>
+        <v>228897</v>
       </c>
       <c r="F18" s="4">
         <v>10768</v>
       </c>
       <c r="G18" s="4">
-        <v>24750</v>
+        <v>25502</v>
       </c>
       <c r="H18" s="4">
-        <v>258664</v>
+        <v>264913</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8243,25 +8260,25 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>177096</v>
+        <v>182808</v>
       </c>
       <c r="C19" s="4">
-        <v>180715</v>
+        <v>186622</v>
       </c>
       <c r="D19" s="4">
-        <v>187292</v>
+        <v>193529</v>
       </c>
       <c r="E19" s="4">
-        <v>245505</v>
+        <v>254672</v>
       </c>
       <c r="F19" s="4">
         <v>10768</v>
       </c>
       <c r="G19" s="4">
-        <v>26700</v>
+        <v>27512</v>
       </c>
       <c r="H19" s="4">
-        <v>284016</v>
+        <v>290967</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8269,25 +8286,25 @@
         <v>20</v>
       </c>
       <c r="B20" s="4">
-        <v>127203</v>
+        <v>131287</v>
       </c>
       <c r="C20" s="4">
-        <v>129601</v>
+        <v>133814</v>
       </c>
       <c r="D20" s="4">
-        <v>133964</v>
+        <v>138396</v>
       </c>
       <c r="E20" s="4">
-        <v>172570</v>
+        <v>178946</v>
       </c>
       <c r="F20" s="4">
         <v>14358</v>
       </c>
       <c r="G20" s="4">
-        <v>20600</v>
+        <v>21226</v>
       </c>
       <c r="H20" s="4">
-        <v>210434</v>
+        <v>215339</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8295,25 +8312,25 @@
         <v>21</v>
       </c>
       <c r="B21" s="4">
-        <v>138472</v>
+        <v>142947</v>
       </c>
       <c r="C21" s="4">
-        <v>141404</v>
+        <v>146037</v>
       </c>
       <c r="D21" s="4">
-        <v>146734</v>
+        <v>151635</v>
       </c>
       <c r="E21" s="4">
-        <v>193915</v>
+        <v>201190</v>
       </c>
       <c r="F21" s="4">
         <v>14358</v>
       </c>
       <c r="G21" s="4">
-        <v>22800</v>
+        <v>23493</v>
       </c>
       <c r="H21" s="4">
-        <v>230456</v>
+        <v>235935</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8321,25 +8338,25 @@
         <v>22</v>
       </c>
       <c r="B22" s="4">
-        <v>157143</v>
+        <v>162258</v>
       </c>
       <c r="C22" s="4">
-        <v>160876</v>
+        <v>166193</v>
       </c>
       <c r="D22" s="4">
-        <v>167663</v>
+        <v>173321</v>
       </c>
       <c r="E22" s="4">
-        <v>227711</v>
+        <v>236391</v>
       </c>
       <c r="F22" s="4">
         <v>14358</v>
       </c>
       <c r="G22" s="4">
-        <v>26100</v>
+        <v>26893</v>
       </c>
       <c r="H22" s="4">
-        <v>262252</v>
+        <v>268646</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8347,25 +8364,25 @@
         <v>23</v>
       </c>
       <c r="B23" s="4">
-        <v>175815</v>
+        <v>181570</v>
       </c>
       <c r="C23" s="4">
-        <v>180343</v>
+        <v>186343</v>
       </c>
       <c r="D23" s="4">
-        <v>188586</v>
+        <v>195001</v>
       </c>
       <c r="E23" s="4">
-        <v>261501</v>
+        <v>271585</v>
       </c>
       <c r="F23" s="4">
         <v>14358</v>
       </c>
       <c r="G23" s="4">
-        <v>29400</v>
+        <v>30294</v>
       </c>
       <c r="H23" s="4">
-        <v>294045</v>
+        <v>301352</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8373,25 +8390,25 @@
         <v>24</v>
       </c>
       <c r="B24" s="4">
-        <v>194302</v>
+        <v>200668</v>
       </c>
       <c r="C24" s="4">
-        <v>199371</v>
+        <v>206011</v>
       </c>
       <c r="D24" s="4">
-        <v>208574</v>
+        <v>215677</v>
       </c>
       <c r="E24" s="4">
-        <v>290071</v>
+        <v>301274</v>
       </c>
       <c r="F24" s="4">
         <v>14358</v>
       </c>
       <c r="G24" s="4">
-        <v>31600</v>
+        <v>32561</v>
       </c>
       <c r="H24" s="4">
-        <v>321292</v>
+        <v>329394</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8399,25 +8416,25 @@
         <v>25</v>
       </c>
       <c r="B25" s="4">
-        <v>139522</v>
+        <v>144042</v>
       </c>
       <c r="C25" s="4">
-        <v>142613</v>
+        <v>147300</v>
       </c>
       <c r="D25" s="4">
-        <v>148216</v>
+        <v>153185</v>
       </c>
       <c r="E25" s="4">
-        <v>197854</v>
+        <v>205321</v>
       </c>
       <c r="F25" s="4">
         <v>17946</v>
       </c>
       <c r="G25" s="4">
-        <v>24250</v>
+        <v>24987</v>
       </c>
       <c r="H25" s="4">
-        <v>237703</v>
+        <v>243280</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8425,25 +8442,25 @@
         <v>26</v>
       </c>
       <c r="B26" s="4">
-        <v>150741</v>
+        <v>155664</v>
       </c>
       <c r="C26" s="4">
-        <v>154512</v>
+        <v>159639</v>
       </c>
       <c r="D26" s="4">
-        <v>161362</v>
+        <v>166833</v>
       </c>
       <c r="E26" s="4">
-        <v>222024</v>
+        <v>230548</v>
       </c>
       <c r="F26" s="4">
         <v>17946</v>
       </c>
       <c r="G26" s="4">
-        <v>26700</v>
+        <v>27512</v>
       </c>
       <c r="H26" s="4">
-        <v>258691</v>
+        <v>264906</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8451,25 +8468,25 @@
         <v>27</v>
       </c>
       <c r="B27" s="4">
-        <v>170487</v>
+        <v>176104</v>
       </c>
       <c r="C27" s="4">
-        <v>175289</v>
+        <v>181165</v>
       </c>
       <c r="D27" s="4">
-        <v>184008</v>
+        <v>190324</v>
       </c>
       <c r="E27" s="4">
-        <v>261214</v>
+        <v>271414</v>
       </c>
       <c r="F27" s="4">
         <v>17946</v>
       </c>
       <c r="G27" s="4">
-        <v>30375</v>
+        <v>31298</v>
       </c>
       <c r="H27" s="4">
-        <v>293104</v>
+        <v>300364</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8477,25 +8494,25 @@
         <v>28</v>
       </c>
       <c r="B28" s="4">
-        <v>190227</v>
+        <v>196537</v>
       </c>
       <c r="C28" s="4">
-        <v>196059</v>
+        <v>202685</v>
       </c>
       <c r="D28" s="4">
-        <v>204060</v>
+        <v>211088</v>
       </c>
       <c r="E28" s="4">
-        <v>300399</v>
+        <v>312274</v>
       </c>
       <c r="F28" s="4">
         <v>17946</v>
       </c>
       <c r="G28" s="4">
-        <v>34050</v>
+        <v>35085</v>
       </c>
       <c r="H28" s="4">
-        <v>327508</v>
+        <v>335816</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8503,25 +8520,25 @@
         <v>29</v>
       </c>
       <c r="B29" s="4">
-        <v>207989</v>
+        <v>214902</v>
       </c>
       <c r="C29" s="4">
-        <v>214502</v>
+        <v>221767</v>
       </c>
       <c r="D29" s="4">
-        <v>224691</v>
+        <v>232468</v>
       </c>
       <c r="E29" s="4">
-        <v>331119</v>
+        <v>344252</v>
       </c>
       <c r="F29" s="4">
         <v>17946</v>
       </c>
       <c r="G29" s="4">
-        <v>36500</v>
+        <v>37610</v>
       </c>
       <c r="H29" s="4">
-        <v>355042</v>
+        <v>364186</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8529,25 +8546,25 @@
         <v>30</v>
       </c>
       <c r="B30" s="4">
-        <v>222327</v>
+        <v>229738</v>
       </c>
       <c r="C30" s="4">
-        <v>229526</v>
+        <v>237326</v>
       </c>
       <c r="D30" s="4">
-        <v>242609</v>
+        <v>251067</v>
       </c>
       <c r="E30" s="4">
-        <v>358422</v>
+        <v>372707</v>
       </c>
       <c r="F30" s="4">
         <v>17946</v>
       </c>
       <c r="G30" s="4">
-        <v>38950</v>
+        <v>40134</v>
       </c>
       <c r="H30" s="4">
-        <v>379156</v>
+        <v>389033</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8555,25 +8572,25 @@
         <v>31</v>
       </c>
       <c r="B31" s="4">
-        <v>237314</v>
+        <v>245243</v>
       </c>
       <c r="C31" s="4">
-        <v>245201</v>
+        <v>253555</v>
       </c>
       <c r="D31" s="4">
-        <v>259530</v>
+        <v>268605</v>
       </c>
       <c r="E31" s="4">
-        <v>386367</v>
+        <v>401824</v>
       </c>
       <c r="F31" s="4">
         <v>17946</v>
       </c>
       <c r="G31" s="4">
-        <v>41400</v>
+        <v>42659</v>
       </c>
       <c r="H31" s="4">
-        <v>403921</v>
+        <v>414549</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8581,25 +8598,25 @@
         <v>32</v>
       </c>
       <c r="B32" s="4">
-        <v>144056</v>
+        <v>148746</v>
       </c>
       <c r="C32" s="4">
-        <v>147484</v>
+        <v>152359</v>
       </c>
       <c r="D32" s="4">
-        <v>153710</v>
+        <v>158899</v>
       </c>
       <c r="E32" s="4">
-        <v>208861</v>
+        <v>216824</v>
       </c>
       <c r="F32" s="4">
         <v>19741</v>
       </c>
       <c r="G32" s="4">
-        <v>26075</v>
+        <v>26868</v>
       </c>
       <c r="H32" s="4">
-        <v>249698</v>
+        <v>255562</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8607,25 +8624,25 @@
         <v>33</v>
       </c>
       <c r="B33" s="4">
-        <v>157405</v>
+        <v>162570</v>
       </c>
       <c r="C33" s="4">
-        <v>161597</v>
+        <v>166987</v>
       </c>
       <c r="D33" s="4">
-        <v>169210</v>
+        <v>174983</v>
       </c>
       <c r="E33" s="4">
-        <v>236612</v>
+        <v>245777</v>
       </c>
       <c r="F33" s="4">
         <v>19741</v>
       </c>
       <c r="G33" s="4">
-        <v>28650</v>
+        <v>29521</v>
       </c>
       <c r="H33" s="4">
-        <v>273334</v>
+        <v>279932</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8633,25 +8650,25 @@
         <v>34</v>
       </c>
       <c r="B34" s="4">
-        <v>180243</v>
+        <v>186205</v>
       </c>
       <c r="C34" s="4">
-        <v>185579</v>
+        <v>191829</v>
       </c>
       <c r="D34" s="4">
-        <v>195265</v>
+        <v>202003</v>
       </c>
       <c r="E34" s="4">
-        <v>281054</v>
+        <v>292108</v>
       </c>
       <c r="F34" s="4">
         <v>19741</v>
       </c>
       <c r="G34" s="4">
-        <v>32513</v>
+        <v>33501</v>
       </c>
       <c r="H34" s="4">
-        <v>311612</v>
+        <v>319400</v>
       </c>
     </row>
     <row r="35" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8659,25 +8676,25 @@
         <v>35</v>
       </c>
       <c r="B35" s="4">
-        <v>196993</v>
+        <v>203568</v>
       </c>
       <c r="C35" s="4">
-        <v>203468</v>
+        <v>210392</v>
       </c>
       <c r="D35" s="4">
-        <v>215227</v>
+        <v>222743</v>
       </c>
       <c r="E35" s="4">
-        <v>319394</v>
+        <v>332151</v>
       </c>
       <c r="F35" s="4">
         <v>19741</v>
       </c>
       <c r="G35" s="4">
-        <v>36375</v>
+        <v>37481</v>
       </c>
       <c r="H35" s="4">
-        <v>343792</v>
+        <v>352584</v>
       </c>
     </row>
     <row r="36" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8685,25 +8702,25 @@
         <v>36</v>
       </c>
       <c r="B36" s="4">
-        <v>235342</v>
+        <v>243221</v>
       </c>
       <c r="C36" s="4">
-        <v>243343</v>
+        <v>251654</v>
       </c>
       <c r="D36" s="4">
-        <v>257876</v>
+        <v>266918</v>
       </c>
       <c r="E36" s="4">
-        <v>386554</v>
+        <v>402071</v>
       </c>
       <c r="F36" s="4">
         <v>19741</v>
       </c>
       <c r="G36" s="4">
-        <v>41525</v>
+        <v>42787</v>
       </c>
       <c r="H36" s="4">
-        <v>402718</v>
+        <v>413336</v>
       </c>
     </row>
     <row r="37" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8711,25 +8728,25 @@
         <v>37</v>
       </c>
       <c r="B37" s="4">
-        <v>253636</v>
+        <v>262140</v>
       </c>
       <c r="C37" s="4">
-        <v>262400</v>
+        <v>271378</v>
       </c>
       <c r="D37" s="4">
-        <v>278319</v>
+        <v>288098</v>
       </c>
       <c r="E37" s="4">
-        <v>419251</v>
+        <v>436120</v>
       </c>
       <c r="F37" s="4">
         <v>19741</v>
       </c>
       <c r="G37" s="4">
-        <v>44100</v>
+        <v>45441</v>
       </c>
       <c r="H37" s="4">
-        <v>431304</v>
+        <v>442810</v>
       </c>
     </row>
     <row r="38" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8737,25 +8754,25 @@
         <v>38</v>
       </c>
       <c r="B38" s="4">
-        <v>152991</v>
+        <v>157983</v>
       </c>
       <c r="C38" s="4">
-        <v>156762</v>
+        <v>161958</v>
       </c>
       <c r="D38" s="4">
-        <v>163612</v>
+        <v>169152</v>
       </c>
       <c r="E38" s="4">
-        <v>224274</v>
+        <v>232867</v>
       </c>
       <c r="F38" s="4">
         <v>21535</v>
       </c>
       <c r="G38" s="4">
-        <v>27900</v>
+        <v>28748</v>
       </c>
       <c r="H38" s="4">
-        <v>266101</v>
+        <v>272385</v>
       </c>
     </row>
     <row r="39" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8763,25 +8780,25 @@
         <v>39</v>
       </c>
       <c r="B39" s="4">
-        <v>165690</v>
+        <v>171144</v>
       </c>
       <c r="C39" s="4">
-        <v>170301</v>
+        <v>176004</v>
       </c>
       <c r="D39" s="4">
-        <v>175510</v>
+        <v>181475</v>
       </c>
       <c r="E39" s="4">
-        <v>252820</v>
+        <v>262676</v>
       </c>
       <c r="F39" s="4">
         <v>21535</v>
       </c>
       <c r="G39" s="4">
-        <v>30600</v>
+        <v>31530</v>
       </c>
       <c r="H39" s="4">
-        <v>289602</v>
+        <v>296634</v>
       </c>
     </row>
     <row r="40" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8789,25 +8806,25 @@
         <v>40</v>
       </c>
       <c r="B40" s="4">
-        <v>187712</v>
+        <v>193949</v>
       </c>
       <c r="C40" s="4">
-        <v>193576</v>
+        <v>200130</v>
       </c>
       <c r="D40" s="4">
-        <v>204235</v>
+        <v>211326</v>
       </c>
       <c r="E40" s="4">
-        <v>298599</v>
+        <v>310437</v>
       </c>
       <c r="F40" s="4">
         <v>21535</v>
       </c>
       <c r="G40" s="4">
-        <v>34650</v>
+        <v>35703</v>
       </c>
       <c r="H40" s="4">
-        <v>327822</v>
+        <v>336068</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8815,25 +8832,25 @@
         <v>41</v>
       </c>
       <c r="B41" s="4">
-        <v>207358</v>
+        <v>214307</v>
       </c>
       <c r="C41" s="4">
-        <v>214488</v>
+        <v>221822</v>
       </c>
       <c r="D41" s="4">
-        <v>227424</v>
+        <v>235409</v>
       </c>
       <c r="E41" s="4">
-        <v>342008</v>
+        <v>355758</v>
       </c>
       <c r="F41" s="4">
         <v>21535</v>
       </c>
       <c r="G41" s="4">
-        <v>38700</v>
+        <v>39876</v>
       </c>
       <c r="H41" s="4">
-        <v>363686</v>
+        <v>373075</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8841,25 +8858,25 @@
         <v>42</v>
       </c>
       <c r="B42" s="4">
-        <v>227164</v>
+        <v>234790</v>
       </c>
       <c r="C42" s="4">
-        <v>235127</v>
+        <v>243183</v>
       </c>
       <c r="D42" s="4">
-        <v>249589</v>
+        <v>258374</v>
       </c>
       <c r="E42" s="4">
-        <v>377654</v>
+        <v>392882</v>
       </c>
       <c r="F42" s="4">
         <v>21535</v>
       </c>
       <c r="G42" s="4">
-        <v>41400</v>
+        <v>42659</v>
       </c>
       <c r="H42" s="4">
-        <v>394286</v>
+        <v>404638</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8867,25 +8884,25 @@
         <v>43</v>
       </c>
       <c r="B43" s="4">
-        <v>247383</v>
+        <v>255700</v>
       </c>
       <c r="C43" s="4">
-        <v>256185</v>
+        <v>264977</v>
       </c>
       <c r="D43" s="4">
-        <v>272168</v>
+        <v>281764</v>
       </c>
       <c r="E43" s="4">
-        <v>413713</v>
+        <v>430431</v>
       </c>
       <c r="F43" s="4">
         <v>21535</v>
       </c>
       <c r="G43" s="4">
-        <v>44100</v>
+        <v>45441</v>
       </c>
       <c r="H43" s="4">
-        <v>425312</v>
+        <v>436642</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8893,25 +8910,25 @@
         <v>44</v>
       </c>
       <c r="B44" s="4">
-        <v>264426</v>
+        <v>273338</v>
       </c>
       <c r="C44" s="4">
-        <v>274062</v>
+        <v>283494</v>
       </c>
       <c r="D44" s="4">
-        <v>291571</v>
+        <v>301884</v>
       </c>
       <c r="E44" s="4">
-        <v>446597</v>
+        <v>464710</v>
       </c>
       <c r="F44" s="4">
         <v>21535</v>
       </c>
       <c r="G44" s="4">
-        <v>46800</v>
+        <v>48223</v>
       </c>
       <c r="H44" s="4">
-        <v>453151</v>
+        <v>465363</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8919,25 +8936,25 @@
         <v>45</v>
       </c>
       <c r="B45" s="4">
-        <v>168468</v>
+        <v>174024</v>
       </c>
       <c r="C45" s="4">
-        <v>173270</v>
+        <v>179085</v>
       </c>
       <c r="D45" s="4">
-        <v>181989</v>
+        <v>188244</v>
       </c>
       <c r="E45" s="4">
-        <v>259195</v>
+        <v>269334</v>
       </c>
       <c r="F45" s="4">
         <v>26919</v>
       </c>
       <c r="G45" s="4">
-        <v>33375</v>
+        <v>34390</v>
       </c>
       <c r="H45" s="4">
-        <v>303984</v>
+        <v>311183</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8945,25 +8962,25 @@
         <v>46</v>
       </c>
       <c r="B46" s="4">
-        <v>182262</v>
+        <v>188333</v>
       </c>
       <c r="C46" s="4">
-        <v>188126</v>
+        <v>194514</v>
       </c>
       <c r="D46" s="4">
-        <v>198785</v>
+        <v>205710</v>
       </c>
       <c r="E46" s="4">
-        <v>293149</v>
+        <v>304821</v>
       </c>
       <c r="F46" s="4">
         <v>26919</v>
       </c>
       <c r="G46" s="4">
-        <v>36450</v>
+        <v>37558</v>
       </c>
       <c r="H46" s="4">
-        <v>330112</v>
+        <v>338192</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8971,25 +8988,25 @@
         <v>47</v>
       </c>
       <c r="B47" s="4">
-        <v>207074</v>
+        <v>214044</v>
       </c>
       <c r="C47" s="4">
-        <v>214547</v>
+        <v>221921</v>
       </c>
       <c r="D47" s="4">
-        <v>228107</v>
+        <v>236163</v>
       </c>
       <c r="E47" s="4">
-        <v>348210</v>
+        <v>362309</v>
       </c>
       <c r="F47" s="4">
         <v>26919</v>
       </c>
       <c r="G47" s="4">
-        <v>41063</v>
+        <v>42311</v>
       </c>
       <c r="H47" s="4">
-        <v>373449</v>
+        <v>382977</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8997,25 +9014,25 @@
         <v>48</v>
       </c>
       <c r="B48" s="4">
-        <v>227167</v>
+        <v>234894</v>
       </c>
       <c r="C48" s="4">
-        <v>236230</v>
+        <v>244447</v>
       </c>
       <c r="D48" s="4">
-        <v>252702</v>
+        <v>261748</v>
       </c>
       <c r="E48" s="4">
-        <v>398538</v>
+        <v>414922</v>
       </c>
       <c r="F48" s="4">
         <v>26919</v>
       </c>
       <c r="G48" s="4">
-        <v>45675</v>
+        <v>47064</v>
       </c>
       <c r="H48" s="4">
-        <v>412037</v>
+        <v>422869</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9023,25 +9040,25 @@
         <v>49</v>
       </c>
       <c r="B49" s="4">
-        <v>248055</v>
+        <v>256513</v>
       </c>
       <c r="C49" s="4">
-        <v>251826</v>
+        <v>260512</v>
       </c>
       <c r="D49" s="4">
-        <v>276598</v>
+        <v>286531</v>
       </c>
       <c r="E49" s="4">
-        <v>439600</v>
+        <v>457734</v>
       </c>
       <c r="F49" s="4">
         <v>26919</v>
       </c>
       <c r="G49" s="4">
-        <v>48750</v>
+        <v>50232</v>
       </c>
       <c r="H49" s="4">
-        <v>432551</v>
+        <v>443840</v>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9049,25 +9066,25 @@
         <v>50</v>
       </c>
       <c r="B50" s="4">
-        <v>270979</v>
+        <v>280230</v>
       </c>
       <c r="C50" s="4">
-        <v>282186</v>
+        <v>292042</v>
       </c>
       <c r="D50" s="4">
-        <v>302531</v>
+        <v>313412</v>
       </c>
       <c r="E50" s="4">
-        <v>482676</v>
+        <v>502620</v>
       </c>
       <c r="F50" s="4">
         <v>26919</v>
       </c>
       <c r="G50" s="4">
-        <v>51825</v>
+        <v>53400</v>
       </c>
       <c r="H50" s="4">
-        <v>480549</v>
+        <v>493635</v>
       </c>
     </row>
     <row r="51" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9075,25 +9092,25 @@
         <v>51</v>
       </c>
       <c r="B51" s="4">
-        <v>287154</v>
+        <v>296994</v>
       </c>
       <c r="C51" s="4">
-        <v>299417</v>
+        <v>309919</v>
       </c>
       <c r="D51" s="4">
-        <v>321702</v>
+        <v>333325</v>
       </c>
       <c r="E51" s="4">
-        <v>519012</v>
+        <v>540563</v>
       </c>
       <c r="F51" s="4">
         <v>26919</v>
       </c>
       <c r="G51" s="4">
-        <v>54900</v>
+        <v>56569</v>
       </c>
       <c r="H51" s="4">
-        <v>509052</v>
+        <v>523092</v>
       </c>
     </row>
     <row r="52" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9101,25 +9118,25 @@
         <v>52</v>
       </c>
       <c r="B52" s="4">
-        <v>224083</v>
+        <v>231485</v>
       </c>
       <c r="C52" s="4">
-        <v>230596</v>
+        <v>238350</v>
       </c>
       <c r="D52" s="4">
-        <v>242432</v>
+        <v>250781</v>
       </c>
       <c r="E52" s="4">
-        <v>347206</v>
+        <v>360827</v>
       </c>
       <c r="F52" s="4">
         <v>35893</v>
       </c>
       <c r="G52" s="4">
-        <v>42500</v>
+        <v>43792</v>
       </c>
       <c r="H52" s="4">
-        <v>396935</v>
+        <v>406568</v>
       </c>
     </row>
     <row r="53" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9127,25 +9144,25 @@
         <v>53</v>
       </c>
       <c r="B53" s="4">
-        <v>246077</v>
+        <v>254278</v>
       </c>
       <c r="C53" s="4">
-        <v>254040</v>
+        <v>262671</v>
       </c>
       <c r="D53" s="4">
-        <v>268502</v>
+        <v>277862</v>
       </c>
       <c r="E53" s="4">
-        <v>396567</v>
+        <v>412370</v>
       </c>
       <c r="F53" s="4">
         <v>35893</v>
       </c>
       <c r="G53" s="4">
-        <v>46200</v>
+        <v>47604</v>
       </c>
       <c r="H53" s="4">
-        <v>433838</v>
+        <v>444765</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9153,25 +9170,25 @@
         <v>54</v>
       </c>
       <c r="B54" s="4">
-        <v>276374</v>
+        <v>285740</v>
       </c>
       <c r="C54" s="4">
-        <v>283980</v>
+        <v>293769</v>
       </c>
       <c r="D54" s="4">
-        <v>302392</v>
+        <v>313108</v>
       </c>
       <c r="E54" s="4">
-        <v>465387</v>
+        <v>484303</v>
       </c>
       <c r="F54" s="4">
         <v>35893</v>
       </c>
       <c r="G54" s="4">
-        <v>51750</v>
+        <v>53323</v>
       </c>
       <c r="H54" s="4">
-        <v>483964</v>
+        <v>496676</v>
       </c>
     </row>
     <row r="55" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9179,25 +9196,25 @@
         <v>55</v>
       </c>
       <c r="B55" s="4">
-        <v>302279</v>
+        <v>312641</v>
       </c>
       <c r="C55" s="4">
-        <v>311520</v>
+        <v>322396</v>
       </c>
       <c r="D55" s="4">
-        <v>333869</v>
+        <v>345869</v>
       </c>
       <c r="E55" s="4">
-        <v>531793</v>
+        <v>553751</v>
       </c>
       <c r="F55" s="4">
         <v>35893</v>
       </c>
       <c r="G55" s="4">
-        <v>57300</v>
+        <v>59042</v>
       </c>
       <c r="H55" s="4">
-        <v>531696</v>
+        <v>546122</v>
       </c>
     </row>
     <row r="56" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9205,25 +9222,25 @@
         <v>56</v>
       </c>
       <c r="B56" s="4">
-        <v>330360</v>
+        <v>341714</v>
       </c>
       <c r="C56" s="4">
-        <v>340689</v>
+        <v>352616</v>
       </c>
       <c r="D56" s="4">
-        <v>365671</v>
+        <v>378855</v>
       </c>
       <c r="E56" s="4">
-        <v>586872</v>
+        <v>611185</v>
       </c>
       <c r="F56" s="4">
         <v>35893</v>
       </c>
       <c r="G56" s="4">
-        <v>61000</v>
+        <v>62854</v>
       </c>
       <c r="H56" s="4">
-        <v>574325</v>
+        <v>590219</v>
       </c>
     </row>
     <row r="57" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9231,25 +9248,25 @@
         <v>57</v>
       </c>
       <c r="B57" s="4">
-        <v>350748</v>
+        <v>362858</v>
       </c>
       <c r="C57" s="4">
-        <v>362164</v>
+        <v>374908</v>
       </c>
       <c r="D57" s="4">
-        <v>389772</v>
+        <v>403906</v>
       </c>
       <c r="E57" s="4">
-        <v>634256</v>
+        <v>660691</v>
       </c>
       <c r="F57" s="4">
         <v>35893</v>
       </c>
       <c r="G57" s="4">
-        <v>64700</v>
+        <v>66667</v>
       </c>
       <c r="H57" s="4">
-        <v>609260</v>
+        <v>626388</v>
       </c>
     </row>
     <row r="58" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9257,25 +9274,25 @@
         <v>58</v>
       </c>
       <c r="B58" s="4">
-        <v>375166</v>
+        <v>388158</v>
       </c>
       <c r="C58" s="4">
-        <v>387670</v>
+        <v>401356</v>
       </c>
       <c r="D58" s="4">
-        <v>417905</v>
+        <v>433112</v>
       </c>
       <c r="E58" s="4">
-        <v>685680</v>
+        <v>714360</v>
       </c>
       <c r="F58" s="4">
         <v>35893</v>
       </c>
       <c r="G58" s="4">
-        <v>68400</v>
+        <v>70479</v>
       </c>
       <c r="H58" s="4">
-        <v>648225</v>
+        <v>666713</v>
       </c>
     </row>
     <row r="59" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9283,25 +9300,25 @@
         <v>59</v>
       </c>
       <c r="B59" s="4">
-        <v>393924</v>
+        <v>407566</v>
       </c>
       <c r="C59" s="4">
-        <v>407054</v>
+        <v>421424</v>
       </c>
       <c r="D59" s="4">
-        <v>438800</v>
+        <v>454768</v>
       </c>
       <c r="E59" s="4">
-        <v>719964</v>
+        <v>750078</v>
       </c>
       <c r="F59" s="4">
         <v>37688</v>
       </c>
       <c r="G59" s="4">
-        <v>71820</v>
+        <v>74003</v>
       </c>
       <c r="H59" s="4">
-        <v>680636</v>
+        <v>700049</v>
       </c>
     </row>
   </sheetData>
@@ -9375,25 +9392,25 @@
         <v>99</v>
       </c>
       <c r="B6" s="4">
-        <v>94002</v>
+        <v>97226</v>
       </c>
       <c r="C6" s="4">
-        <v>94552</v>
+        <v>97803</v>
       </c>
       <c r="D6" s="4">
-        <v>95549</v>
+        <v>98852</v>
       </c>
       <c r="E6" s="4">
-        <v>100375</v>
+        <v>103924</v>
       </c>
       <c r="F6" s="4">
-        <v>94867</v>
+        <v>98135</v>
       </c>
       <c r="G6" s="4">
-        <v>104819</v>
+        <v>108595</v>
       </c>
       <c r="H6" s="4">
-        <v>122504</v>
+        <v>125915</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9401,25 +9418,25 @@
         <v>100</v>
       </c>
       <c r="B7" s="4">
-        <v>99973</v>
+        <v>103415</v>
       </c>
       <c r="C7" s="4">
-        <v>100706</v>
+        <v>104185</v>
       </c>
       <c r="D7" s="4">
-        <v>102040</v>
+        <v>105587</v>
       </c>
       <c r="E7" s="4">
-        <v>108474</v>
+        <v>112350</v>
       </c>
       <c r="F7" s="4">
-        <v>101134</v>
+        <v>104635</v>
       </c>
       <c r="G7" s="4">
-        <v>114408</v>
+        <v>118588</v>
       </c>
       <c r="H7" s="4">
-        <v>132807</v>
+        <v>136500</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9427,25 +9444,25 @@
         <v>101</v>
       </c>
       <c r="B8" s="4">
-        <v>105980</v>
+        <v>109639</v>
       </c>
       <c r="C8" s="4">
-        <v>106896</v>
+        <v>110602</v>
       </c>
       <c r="D8" s="4">
-        <v>108565</v>
+        <v>112356</v>
       </c>
       <c r="E8" s="4">
-        <v>116607</v>
+        <v>120809</v>
       </c>
       <c r="F8" s="4">
-        <v>107435</v>
+        <v>111169</v>
       </c>
       <c r="G8" s="4">
-        <v>124033</v>
+        <v>128614</v>
       </c>
       <c r="H8" s="4">
-        <v>143147</v>
+        <v>147121</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9453,25 +9470,25 @@
         <v>102</v>
       </c>
       <c r="B9" s="4">
-        <v>111966</v>
+        <v>115842</v>
       </c>
       <c r="C9" s="4">
-        <v>113065</v>
+        <v>116998</v>
       </c>
       <c r="D9" s="4">
-        <v>115071</v>
+        <v>119106</v>
       </c>
       <c r="E9" s="4">
-        <v>124721</v>
+        <v>129249</v>
       </c>
       <c r="F9" s="4">
-        <v>113717</v>
+        <v>117682</v>
       </c>
       <c r="G9" s="4">
-        <v>133637</v>
+        <v>138620</v>
       </c>
       <c r="H9" s="4">
-        <v>153465</v>
+        <v>157720</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9479,25 +9496,25 @@
         <v>103</v>
       </c>
       <c r="B10" s="4">
-        <v>117965</v>
+        <v>122060</v>
       </c>
       <c r="C10" s="4">
-        <v>119248</v>
+        <v>123408</v>
       </c>
       <c r="D10" s="4">
-        <v>121589</v>
+        <v>125869</v>
       </c>
       <c r="E10" s="4">
-        <v>132848</v>
+        <v>137703</v>
       </c>
       <c r="F10" s="4">
-        <v>120011</v>
+        <v>124210</v>
       </c>
       <c r="G10" s="4">
-        <v>143254</v>
+        <v>148640</v>
       </c>
       <c r="H10" s="4">
-        <v>163798</v>
+        <v>168333</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9505,25 +9522,25 @@
         <v>104</v>
       </c>
       <c r="B11" s="4">
-        <v>123957</v>
+        <v>128269</v>
       </c>
       <c r="C11" s="4">
-        <v>125423</v>
+        <v>129810</v>
       </c>
       <c r="D11" s="4">
-        <v>128101</v>
+        <v>132624</v>
       </c>
       <c r="E11" s="4">
-        <v>140968</v>
+        <v>146149</v>
       </c>
       <c r="F11" s="4">
-        <v>126299</v>
+        <v>130730</v>
       </c>
       <c r="G11" s="4">
-        <v>152865</v>
+        <v>158653</v>
       </c>
       <c r="H11" s="4">
-        <v>174121</v>
+        <v>178937</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9531,25 +9548,25 @@
         <v>105</v>
       </c>
       <c r="B12" s="4">
-        <v>129930</v>
+        <v>134459</v>
       </c>
       <c r="C12" s="4">
-        <v>131579</v>
+        <v>136192</v>
       </c>
       <c r="D12" s="4">
-        <v>134592</v>
+        <v>139359</v>
       </c>
       <c r="E12" s="4">
-        <v>149068</v>
+        <v>154575</v>
       </c>
       <c r="F12" s="4">
-        <v>132566</v>
+        <v>137230</v>
       </c>
       <c r="G12" s="4">
-        <v>162455</v>
+        <v>168645</v>
       </c>
       <c r="H12" s="4">
-        <v>184427</v>
+        <v>189522</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9557,25 +9574,25 @@
         <v>106</v>
       </c>
       <c r="B13" s="4">
-        <v>99987</v>
+        <v>103429</v>
       </c>
       <c r="C13" s="4">
-        <v>100720</v>
+        <v>104199</v>
       </c>
       <c r="D13" s="4">
-        <v>102054</v>
+        <v>105601</v>
       </c>
       <c r="E13" s="4">
-        <v>108488</v>
+        <v>112364</v>
       </c>
       <c r="F13" s="4">
-        <v>101148</v>
+        <v>104649</v>
       </c>
       <c r="G13" s="4">
-        <v>114422</v>
+        <v>118602</v>
       </c>
       <c r="H13" s="4">
-        <v>132821</v>
+        <v>136514</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9583,25 +9600,25 @@
         <v>107</v>
       </c>
       <c r="B14" s="4">
-        <v>106275</v>
+        <v>109949</v>
       </c>
       <c r="C14" s="4">
-        <v>107242</v>
+        <v>110965</v>
       </c>
       <c r="D14" s="4">
-        <v>109034</v>
+        <v>112849</v>
       </c>
       <c r="E14" s="4">
-        <v>117595</v>
+        <v>121847</v>
       </c>
       <c r="F14" s="4">
-        <v>107812</v>
+        <v>111565</v>
       </c>
       <c r="G14" s="4">
-        <v>125511</v>
+        <v>130168</v>
       </c>
       <c r="H14" s="4">
-        <v>143839</v>
+        <v>147847</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9609,25 +9626,25 @@
         <v>108</v>
       </c>
       <c r="B15" s="4">
-        <v>112546</v>
+        <v>116452</v>
       </c>
       <c r="C15" s="4">
-        <v>113757</v>
+        <v>117725</v>
       </c>
       <c r="D15" s="4">
-        <v>116007</v>
+        <v>120090</v>
       </c>
       <c r="E15" s="4">
-        <v>126696</v>
+        <v>131325</v>
       </c>
       <c r="F15" s="4">
-        <v>114470</v>
+        <v>118474</v>
       </c>
       <c r="G15" s="4">
-        <v>136593</v>
+        <v>141727</v>
       </c>
       <c r="H15" s="4">
-        <v>154849</v>
+        <v>159174</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9635,25 +9652,25 @@
         <v>109</v>
       </c>
       <c r="B16" s="4">
-        <v>118816</v>
+        <v>122955</v>
       </c>
       <c r="C16" s="4">
-        <v>120272</v>
+        <v>124485</v>
       </c>
       <c r="D16" s="4">
-        <v>122980</v>
+        <v>127331</v>
       </c>
       <c r="E16" s="4">
-        <v>135797</v>
+        <v>140803</v>
       </c>
       <c r="F16" s="4">
-        <v>121127</v>
+        <v>125384</v>
       </c>
       <c r="G16" s="4">
-        <v>147675</v>
+        <v>153287</v>
       </c>
       <c r="H16" s="4">
-        <v>165860</v>
+        <v>170501</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9661,25 +9678,25 @@
         <v>110</v>
       </c>
       <c r="B17" s="4">
-        <v>125118</v>
+        <v>129489</v>
       </c>
       <c r="C17" s="4">
-        <v>126808</v>
+        <v>131265</v>
       </c>
       <c r="D17" s="4">
-        <v>129974</v>
+        <v>134593</v>
       </c>
       <c r="E17" s="4">
-        <v>144918</v>
+        <v>150300</v>
       </c>
       <c r="F17" s="4">
-        <v>127805</v>
+        <v>132314</v>
       </c>
       <c r="G17" s="4">
-        <v>158777</v>
+        <v>164867</v>
       </c>
       <c r="H17" s="4">
-        <v>176891</v>
+        <v>181847</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9687,25 +9704,25 @@
         <v>111</v>
       </c>
       <c r="B18" s="4">
-        <v>131388</v>
+        <v>135992</v>
       </c>
       <c r="C18" s="4">
-        <v>133322</v>
+        <v>138025</v>
       </c>
       <c r="D18" s="4">
-        <v>136947</v>
+        <v>141834</v>
       </c>
       <c r="E18" s="4">
-        <v>154018</v>
+        <v>159778</v>
       </c>
       <c r="F18" s="4">
-        <v>134463</v>
+        <v>139223</v>
       </c>
       <c r="G18" s="4">
-        <v>169858</v>
+        <v>176427</v>
       </c>
       <c r="H18" s="4">
-        <v>187900</v>
+        <v>193174</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9713,25 +9730,25 @@
         <v>112</v>
       </c>
       <c r="B19" s="4">
-        <v>137660</v>
+        <v>142495</v>
       </c>
       <c r="C19" s="4">
-        <v>139838</v>
+        <v>144785</v>
       </c>
       <c r="D19" s="4">
-        <v>143920</v>
+        <v>149076</v>
       </c>
       <c r="E19" s="4">
-        <v>163120</v>
+        <v>169256</v>
       </c>
       <c r="F19" s="4">
-        <v>141121</v>
+        <v>146133</v>
       </c>
       <c r="G19" s="4">
-        <v>180941</v>
+        <v>187987</v>
       </c>
       <c r="H19" s="4">
-        <v>198912</v>
+        <v>204501</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9739,25 +9756,25 @@
         <v>113</v>
       </c>
       <c r="B20" s="4">
-        <v>105980</v>
+        <v>109639</v>
       </c>
       <c r="C20" s="4">
-        <v>106896</v>
+        <v>110602</v>
       </c>
       <c r="D20" s="4">
-        <v>108565</v>
+        <v>112356</v>
       </c>
       <c r="E20" s="4">
-        <v>116607</v>
+        <v>120809</v>
       </c>
       <c r="F20" s="4">
-        <v>107435</v>
+        <v>111169</v>
       </c>
       <c r="G20" s="4">
-        <v>124033</v>
+        <v>128614</v>
       </c>
       <c r="H20" s="4">
-        <v>143147</v>
+        <v>147121</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9765,25 +9782,25 @@
         <v>114</v>
       </c>
       <c r="B21" s="4">
-        <v>112546</v>
+        <v>116452</v>
       </c>
       <c r="C21" s="4">
-        <v>113757</v>
+        <v>117725</v>
       </c>
       <c r="D21" s="4">
-        <v>116007</v>
+        <v>120090</v>
       </c>
       <c r="E21" s="4">
-        <v>126696</v>
+        <v>131325</v>
       </c>
       <c r="F21" s="4">
-        <v>114470</v>
+        <v>118474</v>
       </c>
       <c r="G21" s="4">
-        <v>136593</v>
+        <v>141727</v>
       </c>
       <c r="H21" s="4">
-        <v>154849</v>
+        <v>159174</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9791,25 +9808,25 @@
         <v>115</v>
       </c>
       <c r="B22" s="4">
-        <v>119101</v>
+        <v>123255</v>
       </c>
       <c r="C22" s="4">
-        <v>120618</v>
+        <v>124849</v>
       </c>
       <c r="D22" s="4">
-        <v>123448</v>
+        <v>127824</v>
       </c>
       <c r="E22" s="4">
-        <v>136784</v>
+        <v>141841</v>
       </c>
       <c r="F22" s="4">
-        <v>121504</v>
+        <v>125780</v>
       </c>
       <c r="G22" s="4">
-        <v>149153</v>
+        <v>154841</v>
       </c>
       <c r="H22" s="4">
-        <v>166552</v>
+        <v>171229</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9817,25 +9834,25 @@
         <v>116</v>
       </c>
       <c r="B23" s="4">
-        <v>125688</v>
+        <v>130088</v>
       </c>
       <c r="C23" s="4">
-        <v>127500</v>
+        <v>131993</v>
       </c>
       <c r="D23" s="4">
-        <v>130910</v>
+        <v>135577</v>
       </c>
       <c r="E23" s="4">
-        <v>146995</v>
+        <v>152483</v>
       </c>
       <c r="F23" s="4">
-        <v>128559</v>
+        <v>133105</v>
       </c>
       <c r="G23" s="4">
-        <v>161733</v>
+        <v>167975</v>
       </c>
       <c r="H23" s="4">
-        <v>178275</v>
+        <v>183303</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9843,25 +9860,25 @@
         <v>117</v>
       </c>
       <c r="B24" s="4">
-        <v>132254</v>
+        <v>136901</v>
       </c>
       <c r="C24" s="4">
-        <v>134361</v>
+        <v>139116</v>
       </c>
       <c r="D24" s="4">
-        <v>138351</v>
+        <v>143311</v>
       </c>
       <c r="E24" s="4">
-        <v>157184</v>
+        <v>163106</v>
       </c>
       <c r="F24" s="4">
-        <v>135593</v>
+        <v>140411</v>
       </c>
       <c r="G24" s="4">
-        <v>174293</v>
+        <v>181088</v>
       </c>
       <c r="H24" s="4">
-        <v>189978</v>
+        <v>195356</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9869,25 +9886,25 @@
         <v>118</v>
       </c>
       <c r="B25" s="4">
-        <v>138820</v>
+        <v>143715</v>
       </c>
       <c r="C25" s="4">
-        <v>141223</v>
+        <v>146240</v>
       </c>
       <c r="D25" s="4">
-        <v>145793</v>
+        <v>151044</v>
       </c>
       <c r="E25" s="4">
-        <v>167375</v>
+        <v>173728</v>
       </c>
       <c r="F25" s="4">
-        <v>142627</v>
+        <v>147717</v>
       </c>
       <c r="G25" s="4">
-        <v>186853</v>
+        <v>194202</v>
       </c>
       <c r="H25" s="4">
-        <v>201682</v>
+        <v>207411</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9895,25 +9912,25 @@
         <v>119</v>
       </c>
       <c r="B26" s="4">
-        <v>145393</v>
+        <v>150534</v>
       </c>
       <c r="C26" s="4">
-        <v>148090</v>
+        <v>153370</v>
       </c>
       <c r="D26" s="4">
-        <v>153241</v>
+        <v>158784</v>
       </c>
       <c r="E26" s="4">
-        <v>177572</v>
+        <v>184357</v>
       </c>
       <c r="F26" s="4">
-        <v>149668</v>
+        <v>155028</v>
       </c>
       <c r="G26" s="4">
-        <v>199420</v>
+        <v>207321</v>
       </c>
       <c r="H26" s="4">
-        <v>213390</v>
+        <v>219472</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9921,25 +9938,25 @@
         <v>120</v>
       </c>
       <c r="B27" s="4">
-        <v>111966</v>
+        <v>115842</v>
       </c>
       <c r="C27" s="4">
-        <v>113065</v>
+        <v>116998</v>
       </c>
       <c r="D27" s="4">
-        <v>115071</v>
+        <v>119106</v>
       </c>
       <c r="E27" s="4">
-        <v>124721</v>
+        <v>129249</v>
       </c>
       <c r="F27" s="4">
-        <v>113717</v>
+        <v>117682</v>
       </c>
       <c r="G27" s="4">
-        <v>133637</v>
+        <v>138620</v>
       </c>
       <c r="H27" s="4">
-        <v>153465</v>
+        <v>157720</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9947,25 +9964,25 @@
         <v>121</v>
       </c>
       <c r="B28" s="4">
-        <v>118816</v>
+        <v>122955</v>
       </c>
       <c r="C28" s="4">
-        <v>120272</v>
+        <v>124485</v>
       </c>
       <c r="D28" s="4">
-        <v>122980</v>
+        <v>127331</v>
       </c>
       <c r="E28" s="4">
-        <v>135797</v>
+        <v>140803</v>
       </c>
       <c r="F28" s="4">
-        <v>121127</v>
+        <v>125384</v>
       </c>
       <c r="G28" s="4">
-        <v>147675</v>
+        <v>153287</v>
       </c>
       <c r="H28" s="4">
-        <v>165860</v>
+        <v>170501</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9973,25 +9990,25 @@
         <v>122</v>
       </c>
       <c r="B29" s="4">
-        <v>125688</v>
+        <v>130088</v>
       </c>
       <c r="C29" s="4">
-        <v>127500</v>
+        <v>131993</v>
       </c>
       <c r="D29" s="4">
-        <v>130910</v>
+        <v>135577</v>
       </c>
       <c r="E29" s="4">
-        <v>146995</v>
+        <v>152483</v>
       </c>
       <c r="F29" s="4">
-        <v>128559</v>
+        <v>133105</v>
       </c>
       <c r="G29" s="4">
-        <v>161733</v>
+        <v>167975</v>
       </c>
       <c r="H29" s="4">
-        <v>178275</v>
+        <v>183303</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9999,25 +10016,25 @@
         <v>123</v>
       </c>
       <c r="B30" s="4">
-        <v>132549</v>
+        <v>137212</v>
       </c>
       <c r="C30" s="4">
-        <v>134707</v>
+        <v>139480</v>
       </c>
       <c r="D30" s="4">
-        <v>138820</v>
+        <v>143803</v>
       </c>
       <c r="E30" s="4">
-        <v>158172</v>
+        <v>164144</v>
       </c>
       <c r="F30" s="4">
-        <v>135969</v>
+        <v>140807</v>
       </c>
       <c r="G30" s="4">
-        <v>175771</v>
+        <v>182642</v>
       </c>
       <c r="H30" s="4">
-        <v>190670</v>
+        <v>196084</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10025,25 +10042,25 @@
         <v>124</v>
       </c>
       <c r="B31" s="4">
-        <v>139400</v>
+        <v>144325</v>
       </c>
       <c r="C31" s="4">
-        <v>141915</v>
+        <v>146968</v>
       </c>
       <c r="D31" s="4">
-        <v>146730</v>
+        <v>152029</v>
       </c>
       <c r="E31" s="4">
-        <v>169350</v>
+        <v>175804</v>
       </c>
       <c r="F31" s="4">
-        <v>143381</v>
+        <v>148508</v>
       </c>
       <c r="G31" s="4">
-        <v>189810</v>
+        <v>197309</v>
       </c>
       <c r="H31" s="4">
-        <v>203066</v>
+        <v>208867</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10051,25 +10068,25 @@
         <v>125</v>
       </c>
       <c r="B32" s="4">
-        <v>146258</v>
+        <v>151444</v>
       </c>
       <c r="C32" s="4">
-        <v>149129</v>
+        <v>154461</v>
       </c>
       <c r="D32" s="4">
-        <v>154646</v>
+        <v>160261</v>
       </c>
       <c r="E32" s="4">
-        <v>180534</v>
+        <v>187471</v>
       </c>
       <c r="F32" s="4">
-        <v>150798</v>
+        <v>156216</v>
       </c>
       <c r="G32" s="4">
-        <v>203854</v>
+        <v>211982</v>
       </c>
       <c r="H32" s="4">
-        <v>215468</v>
+        <v>221654</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10077,25 +10094,25 @@
         <v>126</v>
       </c>
       <c r="B33" s="4">
-        <v>153123</v>
+        <v>158571</v>
       </c>
       <c r="C33" s="4">
-        <v>156350</v>
+        <v>161963</v>
       </c>
       <c r="D33" s="4">
-        <v>162570</v>
+        <v>168500</v>
       </c>
       <c r="E33" s="4">
-        <v>191725</v>
+        <v>199145</v>
       </c>
       <c r="F33" s="4">
-        <v>158223</v>
+        <v>163931</v>
       </c>
       <c r="G33" s="4">
-        <v>217906</v>
+        <v>226663</v>
       </c>
       <c r="H33" s="4">
-        <v>227877</v>
+        <v>234451</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10103,25 +10120,25 @@
         <v>127</v>
       </c>
       <c r="B34" s="4">
-        <v>117951</v>
+        <v>122046</v>
       </c>
       <c r="C34" s="4">
-        <v>119234</v>
+        <v>123394</v>
       </c>
       <c r="D34" s="4">
-        <v>121575</v>
+        <v>125855</v>
       </c>
       <c r="E34" s="4">
-        <v>132834</v>
+        <v>137689</v>
       </c>
       <c r="F34" s="4">
-        <v>119997</v>
+        <v>124196</v>
       </c>
       <c r="G34" s="4">
-        <v>143240</v>
+        <v>148626</v>
       </c>
       <c r="H34" s="4">
-        <v>163784</v>
+        <v>168319</v>
       </c>
     </row>
     <row r="35" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10129,25 +10146,25 @@
         <v>202</v>
       </c>
       <c r="B35" s="4">
-        <v>132254</v>
+        <v>136901</v>
       </c>
       <c r="C35" s="4">
-        <v>134361</v>
+        <v>139116</v>
       </c>
       <c r="D35" s="4">
-        <v>138351</v>
+        <v>143311</v>
       </c>
       <c r="E35" s="4">
-        <v>157184</v>
+        <v>163106</v>
       </c>
       <c r="F35" s="4">
-        <v>135593</v>
+        <v>140411</v>
       </c>
       <c r="G35" s="4">
-        <v>174293</v>
+        <v>181088</v>
       </c>
       <c r="H35" s="4">
-        <v>189978</v>
+        <v>195356</v>
       </c>
     </row>
     <row r="36" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10155,25 +10172,25 @@
         <v>129</v>
       </c>
       <c r="B36" s="4">
-        <v>139400</v>
+        <v>144325</v>
       </c>
       <c r="C36" s="4">
-        <v>141915</v>
+        <v>146968</v>
       </c>
       <c r="D36" s="4">
-        <v>146730</v>
+        <v>152029</v>
       </c>
       <c r="E36" s="4">
-        <v>169350</v>
+        <v>175804</v>
       </c>
       <c r="F36" s="4">
-        <v>143381</v>
+        <v>148508</v>
       </c>
       <c r="G36" s="4">
-        <v>189810</v>
+        <v>197309</v>
       </c>
       <c r="H36" s="4">
-        <v>203066</v>
+        <v>208867</v>
       </c>
     </row>
     <row r="37" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10181,25 +10198,25 @@
         <v>130</v>
       </c>
       <c r="B37" s="4">
-        <v>146543</v>
+        <v>151743</v>
       </c>
       <c r="C37" s="4">
-        <v>149475</v>
+        <v>154825</v>
       </c>
       <c r="D37" s="4">
-        <v>155115</v>
+        <v>160753</v>
       </c>
       <c r="E37" s="4">
-        <v>181522</v>
+        <v>188509</v>
       </c>
       <c r="F37" s="4">
-        <v>151175</v>
+        <v>156612</v>
       </c>
       <c r="G37" s="4">
-        <v>205333</v>
+        <v>213536</v>
       </c>
       <c r="H37" s="4">
-        <v>216160</v>
+        <v>222382</v>
       </c>
     </row>
     <row r="38" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10207,25 +10224,25 @@
         <v>131</v>
       </c>
       <c r="B38" s="4">
-        <v>153693</v>
+        <v>159170</v>
       </c>
       <c r="C38" s="4">
-        <v>157042</v>
+        <v>162690</v>
       </c>
       <c r="D38" s="4">
-        <v>163506</v>
+        <v>169485</v>
       </c>
       <c r="E38" s="4">
-        <v>193700</v>
+        <v>201221</v>
       </c>
       <c r="F38" s="4">
-        <v>158976</v>
+        <v>164723</v>
       </c>
       <c r="G38" s="4">
-        <v>220862</v>
+        <v>229771</v>
       </c>
       <c r="H38" s="4">
-        <v>229261</v>
+        <v>235905</v>
       </c>
     </row>
     <row r="39" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10233,25 +10250,25 @@
         <v>132</v>
       </c>
       <c r="B39" s="4">
-        <v>160828</v>
+        <v>166582</v>
       </c>
       <c r="C39" s="4">
-        <v>164595</v>
+        <v>170541</v>
       </c>
       <c r="D39" s="4">
-        <v>171884</v>
+        <v>178202</v>
       </c>
       <c r="E39" s="4">
-        <v>205865</v>
+        <v>213918</v>
       </c>
       <c r="F39" s="4">
-        <v>166763</v>
+        <v>172820</v>
       </c>
       <c r="G39" s="4">
-        <v>236378</v>
+        <v>245990</v>
       </c>
       <c r="H39" s="4">
-        <v>242347</v>
+        <v>249414</v>
       </c>
     </row>
     <row r="40" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10259,25 +10276,25 @@
         <v>133</v>
       </c>
       <c r="B40" s="4">
-        <v>123957</v>
+        <v>128269</v>
       </c>
       <c r="C40" s="4">
-        <v>125423</v>
+        <v>129810</v>
       </c>
       <c r="D40" s="4">
-        <v>128101</v>
+        <v>132624</v>
       </c>
       <c r="E40" s="4">
-        <v>140968</v>
+        <v>146149</v>
       </c>
       <c r="F40" s="4">
-        <v>126299</v>
+        <v>130730</v>
       </c>
       <c r="G40" s="4">
-        <v>152865</v>
+        <v>158653</v>
       </c>
       <c r="H40" s="4">
-        <v>174121</v>
+        <v>178937</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10285,25 +10302,25 @@
         <v>134</v>
       </c>
       <c r="B41" s="4">
-        <v>131388</v>
+        <v>135992</v>
       </c>
       <c r="C41" s="4">
-        <v>133322</v>
+        <v>138025</v>
       </c>
       <c r="D41" s="4">
-        <v>136947</v>
+        <v>141834</v>
       </c>
       <c r="E41" s="4">
-        <v>154018</v>
+        <v>159778</v>
       </c>
       <c r="F41" s="4">
-        <v>134463</v>
+        <v>139223</v>
       </c>
       <c r="G41" s="4">
-        <v>169858</v>
+        <v>176427</v>
       </c>
       <c r="H41" s="4">
-        <v>187900</v>
+        <v>193174</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10311,25 +10328,25 @@
         <v>135</v>
       </c>
       <c r="B42" s="4">
-        <v>138820</v>
+        <v>143715</v>
       </c>
       <c r="C42" s="4">
-        <v>141223</v>
+        <v>146240</v>
       </c>
       <c r="D42" s="4">
-        <v>145793</v>
+        <v>151044</v>
       </c>
       <c r="E42" s="4">
-        <v>167375</v>
+        <v>173728</v>
       </c>
       <c r="F42" s="4">
-        <v>142627</v>
+        <v>147717</v>
       </c>
       <c r="G42" s="4">
-        <v>186853</v>
+        <v>194202</v>
       </c>
       <c r="H42" s="4">
-        <v>201682</v>
+        <v>207411</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10337,25 +10354,25 @@
         <v>136</v>
       </c>
       <c r="B43" s="4">
-        <v>146258</v>
+        <v>151444</v>
       </c>
       <c r="C43" s="4">
-        <v>149129</v>
+        <v>154461</v>
       </c>
       <c r="D43" s="4">
-        <v>154646</v>
+        <v>160261</v>
       </c>
       <c r="E43" s="4">
-        <v>180534</v>
+        <v>187471</v>
       </c>
       <c r="F43" s="4">
-        <v>150798</v>
+        <v>156216</v>
       </c>
       <c r="G43" s="4">
-        <v>203854</v>
+        <v>211982</v>
       </c>
       <c r="H43" s="4">
-        <v>215468</v>
+        <v>221654</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10363,25 +10380,25 @@
         <v>137</v>
       </c>
       <c r="B44" s="4">
-        <v>153693</v>
+        <v>159170</v>
       </c>
       <c r="C44" s="4">
-        <v>157042</v>
+        <v>162690</v>
       </c>
       <c r="D44" s="4">
-        <v>163506</v>
+        <v>169485</v>
       </c>
       <c r="E44" s="4">
-        <v>193700</v>
+        <v>201221</v>
       </c>
       <c r="F44" s="4">
-        <v>158976</v>
+        <v>164723</v>
       </c>
       <c r="G44" s="4">
-        <v>220862</v>
+        <v>229771</v>
       </c>
       <c r="H44" s="4">
-        <v>229261</v>
+        <v>235905</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10389,25 +10406,25 @@
         <v>138</v>
       </c>
       <c r="B45" s="4">
-        <v>161124</v>
+        <v>166892</v>
       </c>
       <c r="C45" s="4">
-        <v>164941</v>
+        <v>170904</v>
       </c>
       <c r="D45" s="4">
-        <v>172352</v>
+        <v>178694</v>
       </c>
       <c r="E45" s="4">
-        <v>206852</v>
+        <v>214956</v>
       </c>
       <c r="F45" s="4">
-        <v>167140</v>
+        <v>173216</v>
       </c>
       <c r="G45" s="4">
-        <v>237856</v>
+        <v>247544</v>
       </c>
       <c r="H45" s="4">
-        <v>243039</v>
+        <v>250140</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10415,25 +10432,25 @@
         <v>139</v>
       </c>
       <c r="B46" s="4">
-        <v>168561</v>
+        <v>174622</v>
       </c>
       <c r="C46" s="4">
-        <v>172847</v>
+        <v>179126</v>
       </c>
       <c r="D46" s="4">
-        <v>181195</v>
+        <v>187900</v>
       </c>
       <c r="E46" s="4">
-        <v>220011</v>
+        <v>228700</v>
       </c>
       <c r="F46" s="4">
-        <v>175311</v>
+        <v>181716</v>
       </c>
       <c r="G46" s="4">
-        <v>254857</v>
+        <v>265326</v>
       </c>
       <c r="H46" s="4">
-        <v>256825</v>
+        <v>264384</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10441,25 +10458,25 @@
         <v>140</v>
       </c>
       <c r="B47" s="4">
-        <v>129943</v>
+        <v>134473</v>
       </c>
       <c r="C47" s="4">
-        <v>131592</v>
+        <v>136206</v>
       </c>
       <c r="D47" s="4">
-        <v>134605</v>
+        <v>139373</v>
       </c>
       <c r="E47" s="4">
-        <v>149081</v>
+        <v>154589</v>
       </c>
       <c r="F47" s="4">
-        <v>132579</v>
+        <v>137244</v>
       </c>
       <c r="G47" s="4">
-        <v>162468</v>
+        <v>168659</v>
       </c>
       <c r="H47" s="4">
-        <v>184440</v>
+        <v>189536</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10467,25 +10484,25 @@
         <v>141</v>
       </c>
       <c r="B48" s="4">
-        <v>137660</v>
+        <v>142495</v>
       </c>
       <c r="C48" s="4">
-        <v>139838</v>
+        <v>144785</v>
       </c>
       <c r="D48" s="4">
-        <v>143920</v>
+        <v>149076</v>
       </c>
       <c r="E48" s="4">
-        <v>163120</v>
+        <v>169256</v>
       </c>
       <c r="F48" s="4">
-        <v>141121</v>
+        <v>146133</v>
       </c>
       <c r="G48" s="4">
-        <v>180941</v>
+        <v>187987</v>
       </c>
       <c r="H48" s="4">
-        <v>198912</v>
+        <v>204501</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10493,25 +10510,25 @@
         <v>142</v>
       </c>
       <c r="B49" s="4">
-        <v>145393</v>
+        <v>150534</v>
       </c>
       <c r="C49" s="4">
-        <v>148090</v>
+        <v>153370</v>
       </c>
       <c r="D49" s="4">
-        <v>153241</v>
+        <v>158784</v>
       </c>
       <c r="E49" s="4">
-        <v>177572</v>
+        <v>184357</v>
       </c>
       <c r="F49" s="4">
-        <v>149668</v>
+        <v>155028</v>
       </c>
       <c r="G49" s="4">
-        <v>199420</v>
+        <v>207321</v>
       </c>
       <c r="H49" s="4">
-        <v>213390</v>
+        <v>219472</v>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10519,25 +10536,25 @@
         <v>143</v>
       </c>
       <c r="B50" s="4">
-        <v>153123</v>
+        <v>158571</v>
       </c>
       <c r="C50" s="4">
-        <v>156350</v>
+        <v>161963</v>
       </c>
       <c r="D50" s="4">
-        <v>162570</v>
+        <v>168500</v>
       </c>
       <c r="E50" s="4">
-        <v>191725</v>
+        <v>199145</v>
       </c>
       <c r="F50" s="4">
-        <v>158223</v>
+        <v>163931</v>
       </c>
       <c r="G50" s="4">
-        <v>217906</v>
+        <v>226663</v>
       </c>
       <c r="H50" s="4">
-        <v>227877</v>
+        <v>234451</v>
       </c>
     </row>
     <row r="51" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10545,25 +10562,25 @@
         <v>144</v>
       </c>
       <c r="B51" s="4">
-        <v>160828</v>
+        <v>166582</v>
       </c>
       <c r="C51" s="4">
-        <v>164595</v>
+        <v>170541</v>
       </c>
       <c r="D51" s="4">
-        <v>171884</v>
+        <v>178202</v>
       </c>
       <c r="E51" s="4">
-        <v>205865</v>
+        <v>213918</v>
       </c>
       <c r="F51" s="4">
-        <v>166763</v>
+        <v>172820</v>
       </c>
       <c r="G51" s="4">
-        <v>236378</v>
+        <v>245990</v>
       </c>
       <c r="H51" s="4">
-        <v>242347</v>
+        <v>249414</v>
       </c>
     </row>
     <row r="52" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10571,25 +10588,25 @@
         <v>145</v>
       </c>
       <c r="B52" s="4">
-        <v>168561</v>
+        <v>174622</v>
       </c>
       <c r="C52" s="4">
-        <v>172847</v>
+        <v>179126</v>
       </c>
       <c r="D52" s="4">
-        <v>181195</v>
+        <v>187900</v>
       </c>
       <c r="E52" s="4">
-        <v>220011</v>
+        <v>228700</v>
       </c>
       <c r="F52" s="4">
-        <v>175311</v>
+        <v>181716</v>
       </c>
       <c r="G52" s="4">
-        <v>254857</v>
+        <v>265326</v>
       </c>
       <c r="H52" s="4">
-        <v>256825</v>
+        <v>264384</v>
       </c>
     </row>
     <row r="53" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10597,25 +10614,25 @@
         <v>25</v>
       </c>
       <c r="B53" s="4">
-        <v>176288</v>
+        <v>182655</v>
       </c>
       <c r="C53" s="4">
-        <v>180564</v>
+        <v>187149</v>
       </c>
       <c r="D53" s="4">
-        <v>190500</v>
+        <v>197592</v>
       </c>
       <c r="E53" s="4">
-        <v>233612</v>
+        <v>242907</v>
       </c>
       <c r="F53" s="4">
-        <v>183852</v>
+        <v>190605</v>
       </c>
       <c r="G53" s="4">
-        <v>273330</v>
+        <v>284654</v>
       </c>
       <c r="H53" s="4">
-        <v>270239</v>
+        <v>278237</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10623,25 +10640,25 @@
         <v>146</v>
       </c>
       <c r="B54" s="4">
-        <v>135929</v>
+        <v>140676</v>
       </c>
       <c r="C54" s="4">
-        <v>137761</v>
+        <v>142602</v>
       </c>
       <c r="D54" s="4">
-        <v>141121</v>
+        <v>146133</v>
       </c>
       <c r="E54" s="4">
-        <v>157164</v>
+        <v>162996</v>
       </c>
       <c r="F54" s="4">
-        <v>138820</v>
+        <v>143715</v>
       </c>
       <c r="G54" s="4">
-        <v>171999</v>
+        <v>178588</v>
       </c>
       <c r="H54" s="4">
-        <v>194758</v>
+        <v>200135</v>
       </c>
     </row>
     <row r="55" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10649,25 +10666,25 @@
         <v>147</v>
       </c>
       <c r="B55" s="4">
-        <v>143947</v>
+        <v>149015</v>
       </c>
       <c r="C55" s="4">
-        <v>146380</v>
+        <v>151572</v>
       </c>
       <c r="D55" s="4">
-        <v>150859</v>
+        <v>156280</v>
       </c>
       <c r="E55" s="4">
-        <v>172258</v>
+        <v>178772</v>
       </c>
       <c r="F55" s="4">
-        <v>147795</v>
+        <v>153059</v>
       </c>
       <c r="G55" s="4">
-        <v>192042</v>
+        <v>199566</v>
       </c>
       <c r="H55" s="4">
-        <v>209970</v>
+        <v>215876</v>
       </c>
     </row>
     <row r="56" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10675,25 +10692,25 @@
         <v>148</v>
       </c>
       <c r="B56" s="4">
-        <v>151972</v>
+        <v>157362</v>
       </c>
       <c r="C56" s="4">
-        <v>155016</v>
+        <v>160561</v>
       </c>
       <c r="D56" s="4">
-        <v>160605</v>
+        <v>166435</v>
       </c>
       <c r="E56" s="4">
-        <v>187358</v>
+        <v>194555</v>
       </c>
       <c r="F56" s="4">
-        <v>156777</v>
+        <v>162412</v>
       </c>
       <c r="G56" s="4">
-        <v>212091</v>
+        <v>220552</v>
       </c>
       <c r="H56" s="4">
-        <v>225209</v>
+        <v>231647</v>
       </c>
     </row>
     <row r="57" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10701,25 +10718,25 @@
         <v>149</v>
       </c>
       <c r="B57" s="4">
-        <v>159983</v>
+        <v>165693</v>
       </c>
       <c r="C57" s="4">
-        <v>163628</v>
+        <v>169524</v>
       </c>
       <c r="D57" s="4">
-        <v>170336</v>
+        <v>176575</v>
       </c>
       <c r="E57" s="4">
-        <v>202444</v>
+        <v>210323</v>
       </c>
       <c r="F57" s="4">
-        <v>165745</v>
+        <v>171750</v>
       </c>
       <c r="G57" s="4">
-        <v>232127</v>
+        <v>241522</v>
       </c>
       <c r="H57" s="4">
-        <v>240413</v>
+        <v>247380</v>
       </c>
     </row>
     <row r="58" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10727,25 +10744,25 @@
         <v>150</v>
       </c>
       <c r="B58" s="4">
-        <v>168001</v>
+        <v>174033</v>
       </c>
       <c r="C58" s="4">
-        <v>172247</v>
+        <v>178495</v>
       </c>
       <c r="D58" s="4">
-        <v>180075</v>
+        <v>186723</v>
       </c>
       <c r="E58" s="4">
-        <v>217537</v>
+        <v>226099</v>
       </c>
       <c r="F58" s="4">
-        <v>174720</v>
+        <v>181095</v>
       </c>
       <c r="G58" s="4">
-        <v>252170</v>
+        <v>262501</v>
       </c>
       <c r="H58" s="4">
-        <v>255625</v>
+        <v>263122</v>
       </c>
     </row>
     <row r="59" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10753,25 +10770,25 @@
         <v>151</v>
       </c>
       <c r="B59" s="4">
-        <v>176014</v>
+        <v>182366</v>
       </c>
       <c r="C59" s="4">
-        <v>180859</v>
+        <v>187459</v>
       </c>
       <c r="D59" s="4">
-        <v>189808</v>
+        <v>196865</v>
       </c>
       <c r="E59" s="4">
-        <v>232625</v>
+        <v>241869</v>
       </c>
       <c r="F59" s="4">
-        <v>183689</v>
+        <v>190434</v>
       </c>
       <c r="G59" s="4">
-        <v>272206</v>
+        <v>283472</v>
       </c>
       <c r="H59" s="4">
-        <v>270829</v>
+        <v>278857</v>
       </c>
     </row>
     <row r="60" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10779,25 +10796,25 @@
         <v>32</v>
       </c>
       <c r="B60" s="4">
-        <v>184046</v>
+        <v>190719</v>
       </c>
       <c r="C60" s="4">
-        <v>189492</v>
+        <v>196443</v>
       </c>
       <c r="D60" s="4">
-        <v>199560</v>
+        <v>207026</v>
       </c>
       <c r="E60" s="4">
-        <v>247732</v>
+        <v>257658</v>
       </c>
       <c r="F60" s="4">
-        <v>192678</v>
+        <v>199792</v>
       </c>
       <c r="G60" s="4">
-        <v>292263</v>
+        <v>304464</v>
       </c>
       <c r="H60" s="4">
-        <v>286055</v>
+        <v>294612</v>
       </c>
     </row>
     <row r="61" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10805,25 +10822,25 @@
         <v>152</v>
       </c>
       <c r="B61" s="4">
-        <v>141074</v>
+        <v>146010</v>
       </c>
       <c r="C61" s="4">
-        <v>143080</v>
+        <v>148118</v>
       </c>
       <c r="D61" s="4">
-        <v>146775</v>
+        <v>152002</v>
       </c>
       <c r="E61" s="4">
-        <v>164427</v>
+        <v>170556</v>
       </c>
       <c r="F61" s="4">
-        <v>144240</v>
+        <v>149338</v>
       </c>
       <c r="G61" s="4">
-        <v>180740</v>
+        <v>187702</v>
       </c>
       <c r="H61" s="4">
-        <v>204227</v>
+        <v>209854</v>
       </c>
     </row>
     <row r="62" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10831,25 +10848,25 @@
         <v>153</v>
       </c>
       <c r="B62" s="4">
-        <v>149521</v>
+        <v>154798</v>
       </c>
       <c r="C62" s="4">
-        <v>152198</v>
+        <v>157612</v>
       </c>
       <c r="D62" s="4">
-        <v>157125</v>
+        <v>162791</v>
       </c>
       <c r="E62" s="4">
-        <v>180661</v>
+        <v>187529</v>
       </c>
       <c r="F62" s="4">
-        <v>153745</v>
+        <v>159238</v>
       </c>
       <c r="G62" s="4">
-        <v>202416</v>
+        <v>210395</v>
       </c>
       <c r="H62" s="4">
-        <v>220294</v>
+        <v>226494</v>
       </c>
     </row>
     <row r="63" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10857,25 +10874,25 @@
         <v>154</v>
       </c>
       <c r="B63" s="4">
-        <v>158688</v>
+        <v>164329</v>
       </c>
       <c r="C63" s="4">
-        <v>162037</v>
+        <v>167849</v>
       </c>
       <c r="D63" s="4">
-        <v>168196</v>
+        <v>174323</v>
       </c>
       <c r="E63" s="4">
-        <v>197616</v>
+        <v>205246</v>
       </c>
       <c r="F63" s="4">
-        <v>163971</v>
+        <v>169882</v>
       </c>
       <c r="G63" s="4">
-        <v>224813</v>
+        <v>233832</v>
       </c>
       <c r="H63" s="4">
-        <v>237081</v>
+        <v>243875</v>
       </c>
     </row>
     <row r="64" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10883,25 +10900,25 @@
         <v>155</v>
       </c>
       <c r="B64" s="4">
-        <v>167895</v>
+        <v>173903</v>
       </c>
       <c r="C64" s="4">
-        <v>171916</v>
+        <v>178130</v>
       </c>
       <c r="D64" s="4">
-        <v>179307</v>
+        <v>185898</v>
       </c>
       <c r="E64" s="4">
-        <v>214611</v>
+        <v>223006</v>
       </c>
       <c r="F64" s="4">
-        <v>174237</v>
+        <v>180570</v>
       </c>
       <c r="G64" s="4">
-        <v>247250</v>
+        <v>257312</v>
       </c>
       <c r="H64" s="4">
-        <v>253909</v>
+        <v>261302</v>
       </c>
     </row>
     <row r="65" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10909,25 +10926,25 @@
         <v>156</v>
       </c>
       <c r="B65" s="4">
-        <v>174934</v>
+        <v>181235</v>
       </c>
       <c r="C65" s="4">
-        <v>179627</v>
+        <v>186168</v>
       </c>
       <c r="D65" s="4">
-        <v>188250</v>
+        <v>195230</v>
       </c>
       <c r="E65" s="4">
-        <v>229438</v>
+        <v>238523</v>
       </c>
       <c r="F65" s="4">
-        <v>182335</v>
+        <v>189014</v>
       </c>
       <c r="G65" s="4">
-        <v>267519</v>
+        <v>278549</v>
       </c>
       <c r="H65" s="4">
-        <v>268569</v>
+        <v>276486</v>
       </c>
     </row>
     <row r="66" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10935,25 +10952,25 @@
         <v>157</v>
       </c>
       <c r="B66" s="4">
-        <v>182999</v>
+        <v>189627</v>
       </c>
       <c r="C66" s="4">
-        <v>188364</v>
+        <v>195266</v>
       </c>
       <c r="D66" s="4">
-        <v>198218</v>
+        <v>205624</v>
       </c>
       <c r="E66" s="4">
-        <v>245291</v>
+        <v>255101</v>
       </c>
       <c r="F66" s="4">
-        <v>191459</v>
+        <v>198519</v>
       </c>
       <c r="G66" s="4">
-        <v>288814</v>
+        <v>300847</v>
       </c>
       <c r="H66" s="4">
-        <v>284255</v>
+        <v>292729</v>
       </c>
     </row>
     <row r="67" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10961,25 +10978,25 @@
         <v>38</v>
       </c>
       <c r="B67" s="4">
-        <v>191846</v>
+        <v>198829</v>
       </c>
       <c r="C67" s="4">
-        <v>197883</v>
+        <v>205174</v>
       </c>
       <c r="D67" s="4">
-        <v>208969</v>
+        <v>216826</v>
       </c>
       <c r="E67" s="4">
-        <v>261926</v>
+        <v>272487</v>
       </c>
       <c r="F67" s="4">
-        <v>201365</v>
+        <v>208833</v>
       </c>
       <c r="G67" s="4">
-        <v>310891</v>
+        <v>323954</v>
       </c>
       <c r="H67" s="4">
-        <v>300723</v>
+        <v>309783</v>
       </c>
     </row>
     <row r="68" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10987,25 +11004,25 @@
         <v>158</v>
       </c>
       <c r="B68" s="4">
-        <v>159910</v>
+        <v>165529</v>
       </c>
       <c r="C68" s="4">
-        <v>162466</v>
+        <v>168214</v>
       </c>
       <c r="D68" s="4">
-        <v>167169</v>
+        <v>173158</v>
       </c>
       <c r="E68" s="4">
-        <v>189636</v>
+        <v>196773</v>
       </c>
       <c r="F68" s="4">
-        <v>163952</v>
+        <v>169777</v>
       </c>
       <c r="G68" s="4">
-        <v>210405</v>
+        <v>218603</v>
       </c>
       <c r="H68" s="4">
-        <v>236061</v>
+        <v>242558</v>
       </c>
     </row>
     <row r="69" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11013,25 +11030,25 @@
         <v>159</v>
       </c>
       <c r="B69" s="4">
-        <v>169075</v>
+        <v>175073</v>
       </c>
       <c r="C69" s="4">
-        <v>172485</v>
+        <v>178657</v>
       </c>
       <c r="D69" s="4">
-        <v>178756</v>
+        <v>185248</v>
       </c>
       <c r="E69" s="4">
-        <v>208706</v>
+        <v>216728</v>
       </c>
       <c r="F69" s="4">
-        <v>174460</v>
+        <v>180733</v>
       </c>
       <c r="G69" s="4">
-        <v>236393</v>
+        <v>245830</v>
       </c>
       <c r="H69" s="4">
-        <v>254077</v>
+        <v>261249</v>
       </c>
     </row>
     <row r="70" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11039,25 +11056,25 @@
         <v>160</v>
       </c>
       <c r="B70" s="4">
-        <v>178253</v>
+        <v>184632</v>
       </c>
       <c r="C70" s="4">
-        <v>182519</v>
+        <v>189115</v>
       </c>
       <c r="D70" s="4">
-        <v>190357</v>
+        <v>197354</v>
       </c>
       <c r="E70" s="4">
-        <v>227789</v>
+        <v>236698</v>
       </c>
       <c r="F70" s="4">
-        <v>184982</v>
+        <v>191704</v>
       </c>
       <c r="G70" s="4">
-        <v>262395</v>
+        <v>273071</v>
       </c>
       <c r="H70" s="4">
-        <v>272109</v>
+        <v>279955</v>
       </c>
     </row>
     <row r="71" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11065,25 +11082,25 @@
         <v>161</v>
       </c>
       <c r="B71" s="4">
-        <v>187389</v>
+        <v>194145</v>
       </c>
       <c r="C71" s="4">
-        <v>192509</v>
+        <v>199528</v>
       </c>
       <c r="D71" s="4">
-        <v>201916</v>
+        <v>209414</v>
       </c>
       <c r="E71" s="4">
-        <v>246830</v>
+        <v>256623</v>
       </c>
       <c r="F71" s="4">
-        <v>195462</v>
+        <v>202631</v>
       </c>
       <c r="G71" s="4">
-        <v>288354</v>
+        <v>300268</v>
       </c>
       <c r="H71" s="4">
-        <v>290096</v>
+        <v>298616</v>
       </c>
     </row>
     <row r="72" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11091,25 +11108,25 @@
         <v>162</v>
       </c>
       <c r="B72" s="4">
-        <v>196582</v>
+        <v>203719</v>
       </c>
       <c r="C72" s="4">
-        <v>202558</v>
+        <v>210000</v>
       </c>
       <c r="D72" s="4">
-        <v>213532</v>
+        <v>221535</v>
       </c>
       <c r="E72" s="4">
-        <v>265928</v>
+        <v>276608</v>
       </c>
       <c r="F72" s="4">
-        <v>205999</v>
+        <v>213617</v>
       </c>
       <c r="G72" s="4">
-        <v>306675</v>
+        <v>319436</v>
       </c>
       <c r="H72" s="4">
-        <v>308142</v>
+        <v>317334</v>
       </c>
     </row>
     <row r="73" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11117,25 +11134,25 @@
         <v>163</v>
       </c>
       <c r="B73" s="4">
-        <v>205757</v>
+        <v>213273</v>
       </c>
       <c r="C73" s="4">
-        <v>212587</v>
+        <v>220453</v>
       </c>
       <c r="D73" s="4">
-        <v>225129</v>
+        <v>233635</v>
       </c>
       <c r="E73" s="4">
-        <v>285008</v>
+        <v>296573</v>
       </c>
       <c r="F73" s="4">
-        <v>216517</v>
+        <v>224583</v>
       </c>
       <c r="G73" s="4">
-        <v>324977</v>
+        <v>338583</v>
       </c>
       <c r="H73" s="4">
-        <v>326168</v>
+        <v>336035</v>
       </c>
     </row>
     <row r="74" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11143,25 +11160,25 @@
         <v>45</v>
       </c>
       <c r="B74" s="4">
-        <v>214923</v>
+        <v>222821</v>
       </c>
       <c r="C74" s="4">
-        <v>222609</v>
+        <v>230900</v>
       </c>
       <c r="D74" s="4">
-        <v>236719</v>
+        <v>245730</v>
       </c>
       <c r="E74" s="4">
-        <v>304080</v>
+        <v>316532</v>
       </c>
       <c r="F74" s="4">
-        <v>227027</v>
+        <v>235543</v>
       </c>
       <c r="G74" s="4">
-        <v>350967</v>
+        <v>365814</v>
       </c>
       <c r="H74" s="4">
-        <v>344188</v>
+        <v>354730</v>
       </c>
     </row>
   </sheetData>
@@ -11238,22 +11255,22 @@
         <v>169</v>
       </c>
       <c r="C6" s="4">
-        <v>289819</v>
+        <v>299248</v>
       </c>
       <c r="D6" s="4">
-        <v>298370</v>
+        <v>308245</v>
       </c>
       <c r="E6" s="4">
-        <v>292534</v>
+        <v>302104</v>
       </c>
       <c r="F6" s="4">
-        <v>339717</v>
+        <v>351752</v>
       </c>
       <c r="G6" s="4">
-        <v>377878</v>
+        <v>391907</v>
       </c>
       <c r="H6" s="4">
-        <v>387353</v>
+        <v>398192</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11264,16 +11281,16 @@
         <v>169</v>
       </c>
       <c r="C7" s="4">
-        <v>317697</v>
+        <v>327976</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>169</v>
       </c>
       <c r="E7" s="4">
-        <v>320412</v>
+        <v>330832</v>
       </c>
       <c r="F7" s="4">
-        <v>367595</v>
+        <v>380480</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>169</v>
@@ -11287,25 +11304,25 @@
         <v>171</v>
       </c>
       <c r="B8" s="4">
-        <v>293964</v>
+        <v>303391</v>
       </c>
       <c r="C8" s="4">
-        <v>298443</v>
+        <v>308104</v>
       </c>
       <c r="D8" s="4">
-        <v>306532</v>
+        <v>316615</v>
       </c>
       <c r="E8" s="4">
-        <v>301006</v>
+        <v>310801</v>
       </c>
       <c r="F8" s="4">
-        <v>345708</v>
+        <v>357839</v>
       </c>
       <c r="G8" s="4">
-        <v>381853</v>
+        <v>395872</v>
       </c>
       <c r="H8" s="4">
-        <v>414725</v>
+        <v>425722</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11313,25 +11330,25 @@
         <v>172</v>
       </c>
       <c r="B9" s="4">
-        <v>333602</v>
+        <v>344009</v>
       </c>
       <c r="C9" s="4">
-        <v>335841</v>
+        <v>346365</v>
       </c>
       <c r="D9" s="4">
-        <v>339885</v>
+        <v>350621</v>
       </c>
       <c r="E9" s="4">
-        <v>337122</v>
+        <v>347713</v>
       </c>
       <c r="F9" s="4">
-        <v>359474</v>
+        <v>371232</v>
       </c>
       <c r="G9" s="4">
-        <v>377546</v>
+        <v>390249</v>
       </c>
       <c r="H9" s="4">
-        <v>393982</v>
+        <v>405174</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11339,7 +11356,7 @@
         <v>173</v>
       </c>
       <c r="B10" s="4">
-        <v>349214</v>
+        <v>360097</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>169</v>
@@ -11348,10 +11365,10 @@
         <v>169</v>
       </c>
       <c r="E10" s="4">
-        <v>352734</v>
+        <v>363801</v>
       </c>
       <c r="F10" s="4">
-        <v>375086</v>
+        <v>387320</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>169</v>
@@ -11365,25 +11382,25 @@
         <v>174</v>
       </c>
       <c r="B11" s="4">
-        <v>345678</v>
+        <v>356352</v>
       </c>
       <c r="C11" s="4">
-        <v>346884</v>
+        <v>357621</v>
       </c>
       <c r="D11" s="4">
-        <v>349137</v>
+        <v>359991</v>
       </c>
       <c r="E11" s="4">
-        <v>347600</v>
+        <v>358375</v>
       </c>
       <c r="F11" s="4">
-        <v>360016</v>
+        <v>371439</v>
       </c>
       <c r="G11" s="4">
-        <v>370056</v>
+        <v>382004</v>
       </c>
       <c r="H11" s="4">
-        <v>386741</v>
+        <v>397849</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11391,7 +11408,7 @@
         <v>175</v>
       </c>
       <c r="B12" s="4">
-        <v>354599</v>
+        <v>365545</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>169</v>
@@ -11400,10 +11417,10 @@
         <v>169</v>
       </c>
       <c r="E12" s="4">
-        <v>356521</v>
+        <v>367568</v>
       </c>
       <c r="F12" s="4">
-        <v>368937</v>
+        <v>380632</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>169</v>
@@ -11417,7 +11434,7 @@
         <v>176</v>
       </c>
       <c r="B13" s="4">
-        <v>363204</v>
+        <v>374285</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>169</v>
@@ -11443,25 +11460,25 @@
         <v>177</v>
       </c>
       <c r="B14" s="4">
-        <v>359250</v>
+        <v>370439</v>
       </c>
       <c r="C14" s="4">
-        <v>361489</v>
+        <v>372795</v>
       </c>
       <c r="D14" s="4">
-        <v>365533</v>
+        <v>377051</v>
       </c>
       <c r="E14" s="4">
-        <v>362770</v>
+        <v>374143</v>
       </c>
       <c r="F14" s="4">
-        <v>385122</v>
+        <v>397662</v>
       </c>
       <c r="G14" s="4">
-        <v>403194</v>
+        <v>416679</v>
       </c>
       <c r="H14" s="4">
-        <v>470030</v>
+        <v>482004</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11469,25 +11486,25 @@
         <v>178</v>
       </c>
       <c r="B15" s="4">
-        <v>355714</v>
+        <v>366694</v>
       </c>
       <c r="C15" s="4">
-        <v>356920</v>
+        <v>367963</v>
       </c>
       <c r="D15" s="4">
-        <v>359173</v>
+        <v>370333</v>
       </c>
       <c r="E15" s="4">
-        <v>357636</v>
+        <v>368717</v>
       </c>
       <c r="F15" s="4">
-        <v>370052</v>
+        <v>381781</v>
       </c>
       <c r="G15" s="4">
-        <v>380092</v>
+        <v>392346</v>
       </c>
       <c r="H15" s="4">
-        <v>421977</v>
+        <v>433391</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11495,25 +11512,25 @@
         <v>179</v>
       </c>
       <c r="B16" s="4">
-        <v>316517</v>
+        <v>326685</v>
       </c>
       <c r="C16" s="4">
-        <v>321340</v>
+        <v>331760</v>
       </c>
       <c r="D16" s="4">
-        <v>330352</v>
+        <v>341243</v>
       </c>
       <c r="E16" s="4">
-        <v>324206</v>
+        <v>334776</v>
       </c>
       <c r="F16" s="4">
-        <v>373869</v>
+        <v>387034</v>
       </c>
       <c r="G16" s="4">
-        <v>414030</v>
+        <v>429293</v>
       </c>
       <c r="H16" s="4">
-        <v>480767</v>
+        <v>492670</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11521,25 +11538,25 @@
         <v>180</v>
       </c>
       <c r="B17" s="4">
-        <v>365050</v>
+        <v>376347</v>
       </c>
       <c r="C17" s="4">
-        <v>366620</v>
+        <v>378000</v>
       </c>
       <c r="D17" s="4">
-        <v>369473</v>
+        <v>381002</v>
       </c>
       <c r="E17" s="4">
-        <v>367551</v>
+        <v>378979</v>
       </c>
       <c r="F17" s="4">
-        <v>383260</v>
+        <v>395509</v>
       </c>
       <c r="G17" s="4">
-        <v>395976</v>
+        <v>408890</v>
       </c>
       <c r="H17" s="4">
-        <v>434831</v>
+        <v>446681</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11547,25 +11564,25 @@
         <v>181</v>
       </c>
       <c r="B18" s="4">
-        <v>369310</v>
+        <v>380666</v>
       </c>
       <c r="C18" s="4">
-        <v>370887</v>
+        <v>382326</v>
       </c>
       <c r="D18" s="4">
-        <v>372686</v>
+        <v>384218</v>
       </c>
       <c r="E18" s="4">
-        <v>371459</v>
+        <v>382928</v>
       </c>
       <c r="F18" s="4">
-        <v>381395</v>
+        <v>393382</v>
       </c>
       <c r="G18" s="4">
-        <v>389419</v>
+        <v>401826</v>
       </c>
       <c r="H18" s="4">
-        <v>410584</v>
+        <v>422320</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11573,7 +11590,7 @@
         <v>182</v>
       </c>
       <c r="B19" s="4">
-        <v>420121</v>
+        <v>433027</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>169</v>
@@ -11582,10 +11599,10 @@
         <v>169</v>
       </c>
       <c r="E19" s="4">
-        <v>422270</v>
+        <v>435289</v>
       </c>
       <c r="F19" s="4">
-        <v>432206</v>
+        <v>445743</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>169</v>
@@ -11599,25 +11616,25 @@
         <v>183</v>
       </c>
       <c r="B20" s="4">
-        <v>351407</v>
+        <v>362484</v>
       </c>
       <c r="C20" s="4">
-        <v>356292</v>
+        <v>367625</v>
       </c>
       <c r="D20" s="4">
-        <v>363044</v>
+        <v>374730</v>
       </c>
       <c r="E20" s="4">
-        <v>358442</v>
+        <v>369887</v>
       </c>
       <c r="F20" s="4">
-        <v>395696</v>
+        <v>409087</v>
       </c>
       <c r="G20" s="4">
-        <v>425818</v>
+        <v>440783</v>
       </c>
       <c r="H20" s="4">
-        <v>511142</v>
+        <v>523588</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11625,25 +11642,25 @@
         <v>184</v>
       </c>
       <c r="B21" s="4">
-        <v>318279</v>
+        <v>328345</v>
       </c>
       <c r="C21" s="4">
-        <v>323164</v>
+        <v>333486</v>
       </c>
       <c r="D21" s="4">
-        <v>329916</v>
+        <v>340591</v>
       </c>
       <c r="E21" s="4">
-        <v>325314</v>
+        <v>335748</v>
       </c>
       <c r="F21" s="4">
-        <v>362568</v>
+        <v>374948</v>
       </c>
       <c r="G21" s="4">
-        <v>392690</v>
+        <v>406644</v>
       </c>
       <c r="H21" s="4">
-        <v>402414</v>
+        <v>413849</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11651,7 +11668,7 @@
         <v>204</v>
       </c>
       <c r="B22" s="4">
-        <v>391082</v>
+        <v>403013</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>169</v>
@@ -11724,13 +11741,13 @@
         <v>206</v>
       </c>
       <c r="B6" s="4">
-        <v>160620</v>
+        <v>211328</v>
       </c>
       <c r="C6" s="4">
-        <v>239010</v>
+        <v>328467</v>
       </c>
       <c r="D6" s="4">
-        <v>196631</v>
+        <v>166591</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11738,13 +11755,13 @@
         <v>207</v>
       </c>
       <c r="B7" s="4">
-        <v>173879</v>
+        <v>230195</v>
       </c>
       <c r="C7" s="4">
-        <v>262540</v>
+        <v>366471</v>
       </c>
       <c r="D7" s="4">
-        <v>218190</v>
+        <v>180363</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11752,13 +11769,13 @@
         <v>208</v>
       </c>
       <c r="B8" s="4">
-        <v>187429</v>
+        <v>247558</v>
       </c>
       <c r="C8" s="4">
-        <v>288104</v>
+        <v>406555</v>
       </c>
       <c r="D8" s="4">
-        <v>241704</v>
+        <v>194464</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11766,13 +11783,13 @@
         <v>209</v>
       </c>
       <c r="B9" s="4">
-        <v>196626</v>
+        <v>259301</v>
       </c>
       <c r="C9" s="4">
-        <v>305312</v>
+        <v>433442</v>
       </c>
       <c r="D9" s="4">
-        <v>257538</v>
+        <v>204036</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11780,13 +11797,13 @@
         <v>132</v>
       </c>
       <c r="B10" s="4">
-        <v>169356</v>
+        <v>224626</v>
       </c>
       <c r="C10" s="4">
-        <v>253794</v>
+        <v>352151</v>
       </c>
       <c r="D10" s="4">
-        <v>209446</v>
+        <v>175651</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11794,13 +11811,13 @@
         <v>210</v>
       </c>
       <c r="B11" s="4">
-        <v>179639</v>
+        <v>236516</v>
       </c>
       <c r="C11" s="4">
-        <v>273033</v>
+        <v>382510</v>
       </c>
       <c r="D11" s="4">
-        <v>228581</v>
+        <v>186363</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11808,13 +11825,13 @@
         <v>211</v>
       </c>
       <c r="B12" s="4">
-        <v>195376</v>
+        <v>255930</v>
       </c>
       <c r="C12" s="4">
-        <v>300990</v>
+        <v>425825</v>
       </c>
       <c r="D12" s="4">
-        <v>255197</v>
+        <v>202733</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11822,13 +11839,13 @@
         <v>212</v>
       </c>
       <c r="B13" s="4">
-        <v>210338</v>
+        <v>273293</v>
       </c>
       <c r="C13" s="4">
-        <v>329379</v>
+        <v>470864</v>
       </c>
       <c r="D13" s="4">
-        <v>283418</v>
+        <v>218321</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11836,13 +11853,13 @@
         <v>213</v>
       </c>
       <c r="B14" s="4">
-        <v>220479</v>
+        <v>285036</v>
       </c>
       <c r="C14" s="4">
-        <v>348475</v>
+        <v>501082</v>
       </c>
       <c r="D14" s="4">
-        <v>302419</v>
+        <v>228885</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11850,13 +11867,13 @@
         <v>25</v>
       </c>
       <c r="B15" s="4">
-        <v>188034</v>
+        <v>250361</v>
       </c>
       <c r="C15" s="4">
-        <v>286607</v>
+        <v>400226</v>
       </c>
       <c r="D15" s="4">
-        <v>235732</v>
+        <v>195056</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11864,13 +11881,13 @@
         <v>26</v>
       </c>
       <c r="B16" s="4">
-        <v>199261</v>
+        <v>262251</v>
       </c>
       <c r="C16" s="4">
-        <v>307734</v>
+        <v>428036</v>
       </c>
       <c r="D16" s="4">
-        <v>252446</v>
+        <v>206761</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11878,13 +11895,13 @@
         <v>27</v>
       </c>
       <c r="B17" s="4">
-        <v>216873</v>
+        <v>281665</v>
       </c>
       <c r="C17" s="4">
-        <v>339441</v>
+        <v>470206</v>
       </c>
       <c r="D17" s="4">
-        <v>277973</v>
+        <v>225103</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11892,13 +11909,13 @@
         <v>28</v>
       </c>
       <c r="B18" s="4">
-        <v>230434</v>
+        <v>296108</v>
       </c>
       <c r="C18" s="4">
-        <v>367847</v>
+        <v>519665</v>
       </c>
       <c r="D18" s="4">
-        <v>310351</v>
+        <v>239265</v>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11906,13 +11923,13 @@
         <v>29</v>
       </c>
       <c r="B19" s="4">
-        <v>244340</v>
+        <v>310771</v>
       </c>
       <c r="C19" s="4">
-        <v>391653</v>
+        <v>552279</v>
       </c>
       <c r="D19" s="4">
-        <v>331673</v>
+        <v>253742</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11920,13 +11937,13 @@
         <v>32</v>
       </c>
       <c r="B20" s="4">
-        <v>198231</v>
+        <v>263630</v>
       </c>
       <c r="C20" s="4">
-        <v>304341</v>
+        <v>434179</v>
       </c>
       <c r="D20" s="4">
-        <v>258306</v>
+        <v>205653</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11934,13 +11951,13 @@
         <v>33</v>
       </c>
       <c r="B21" s="4">
-        <v>209450</v>
+        <v>275520</v>
       </c>
       <c r="C21" s="4">
-        <v>325452</v>
+        <v>461505</v>
       </c>
       <c r="D21" s="4">
-        <v>274559</v>
+        <v>217351</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11948,13 +11965,13 @@
         <v>34</v>
       </c>
       <c r="B22" s="4">
-        <v>227069</v>
+        <v>294941</v>
       </c>
       <c r="C22" s="4">
-        <v>357166</v>
+        <v>503805</v>
       </c>
       <c r="D22" s="4">
-        <v>300210</v>
+        <v>235700</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11962,13 +11979,13 @@
         <v>35</v>
       </c>
       <c r="B23" s="4">
-        <v>240622</v>
+        <v>309377</v>
       </c>
       <c r="C23" s="4">
-        <v>385564</v>
+        <v>553611</v>
       </c>
       <c r="D23" s="4">
-        <v>332917</v>
+        <v>249854</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11976,13 +11993,13 @@
         <v>79</v>
       </c>
       <c r="B24" s="4">
-        <v>254535</v>
+        <v>324048</v>
       </c>
       <c r="C24" s="4">
-        <v>409377</v>
+        <v>585810</v>
       </c>
       <c r="D24" s="4">
-        <v>353844</v>
+        <v>264340</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11990,13 +12007,13 @@
         <v>38</v>
       </c>
       <c r="B25" s="4">
-        <v>208215</v>
+        <v>276688</v>
       </c>
       <c r="C25" s="4">
-        <v>321854</v>
+        <v>467607</v>
       </c>
       <c r="D25" s="4">
-        <v>280376</v>
+        <v>216032</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12004,13 +12021,13 @@
         <v>39</v>
       </c>
       <c r="B26" s="4">
-        <v>219666</v>
+        <v>288818</v>
       </c>
       <c r="C26" s="4">
-        <v>343197</v>
+        <v>495453</v>
       </c>
       <c r="D26" s="4">
-        <v>297127</v>
+        <v>227969</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12018,13 +12035,13 @@
         <v>40</v>
       </c>
       <c r="B27" s="4">
-        <v>238598</v>
+        <v>309663</v>
       </c>
       <c r="C27" s="4">
-        <v>376162</v>
+        <v>539347</v>
       </c>
       <c r="D27" s="4">
-        <v>324315</v>
+        <v>247677</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12032,13 +12049,13 @@
         <v>41</v>
       </c>
       <c r="B28" s="4">
-        <v>250784</v>
+        <v>322617</v>
       </c>
       <c r="C28" s="4">
-        <v>403256</v>
+        <v>587167</v>
       </c>
       <c r="D28" s="4">
-        <v>355112</v>
+        <v>260415</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12046,13 +12063,13 @@
         <v>42</v>
       </c>
       <c r="B29" s="4">
-        <v>264950</v>
+        <v>337550</v>
       </c>
       <c r="C29" s="4">
-        <v>427321</v>
+        <v>619614</v>
       </c>
       <c r="D29" s="4">
-        <v>376281</v>
+        <v>275163</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12060,13 +12077,13 @@
         <v>45</v>
       </c>
       <c r="B30" s="4">
-        <v>244220</v>
+        <v>322955</v>
       </c>
       <c r="C30" s="4">
-        <v>379647</v>
+        <v>547698</v>
       </c>
       <c r="D30" s="4">
-        <v>327507</v>
+        <v>253420</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12074,13 +12091,13 @@
         <v>46</v>
       </c>
       <c r="B31" s="4">
-        <v>258390</v>
+        <v>335509</v>
       </c>
       <c r="C31" s="4">
-        <v>406018</v>
+        <v>590374</v>
       </c>
       <c r="D31" s="4">
-        <v>358359</v>
+        <v>268210</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12088,13 +12105,13 @@
         <v>47</v>
       </c>
       <c r="B32" s="4">
-        <v>280594</v>
+        <v>356332</v>
       </c>
       <c r="C32" s="4">
-        <v>445548</v>
+        <v>656163</v>
       </c>
       <c r="D32" s="4">
-        <v>406355</v>
+        <v>291362</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12102,13 +12119,13 @@
         <v>48</v>
       </c>
       <c r="B33" s="4">
-        <v>296745</v>
+        <v>369782</v>
       </c>
       <c r="C33" s="4">
-        <v>480093</v>
+        <v>714783</v>
       </c>
       <c r="D33" s="4">
-        <v>447424</v>
+        <v>308264</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12116,13 +12133,13 @@
         <v>49</v>
       </c>
       <c r="B34" s="4">
-        <v>312428</v>
+        <v>383832</v>
       </c>
       <c r="C34" s="4">
-        <v>508046</v>
+        <v>758956</v>
       </c>
       <c r="D34" s="4">
-        <v>479720</v>
+        <v>324623</v>
       </c>
     </row>
   </sheetData>
